--- a/research/traditional_assets/database/data/jordan/jordan_tobacco.xlsx
+++ b/research/traditional_assets/database/data/jordan/jordan_tobacco.xlsx
@@ -588,34 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.187</v>
+        <v>-0.221</v>
       </c>
       <c r="G2">
-        <v>-0.3459016393442623</v>
+        <v>-1.053608247422681</v>
       </c>
       <c r="H2">
-        <v>-0.3459016393442623</v>
+        <v>-1.053608247422681</v>
       </c>
       <c r="I2">
-        <v>-0.3942622950819672</v>
+        <v>-1.177319587628866</v>
       </c>
       <c r="J2">
-        <v>-0.3942622950819672</v>
+        <v>-1.177319587628866</v>
       </c>
       <c r="K2">
-        <v>-7.24</v>
+        <v>-0.995</v>
       </c>
       <c r="L2">
-        <v>-0.5934426229508197</v>
+        <v>-0.2051546391752578</v>
       </c>
       <c r="M2">
-        <v>6.51</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.1109028960817717</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.899171270718232</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,79 +627,76 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>6.51</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>1.86</v>
+        <v>7.24</v>
       </c>
       <c r="V2">
-        <v>0.03168654173764907</v>
+        <v>0.7098039215686275</v>
       </c>
       <c r="W2">
-        <v>-4.641025641025641</v>
+        <v>-0.3579136690647483</v>
       </c>
       <c r="X2">
-        <v>0.1197171494289259</v>
+        <v>0.3547058643832672</v>
       </c>
       <c r="Y2">
-        <v>-4.760742790454567</v>
+        <v>-0.7126195334480154</v>
       </c>
       <c r="Z2">
-        <v>0.2255917159763313</v>
+        <v>0.1793174843790439</v>
       </c>
       <c r="AA2">
-        <v>-0.08894230769230768</v>
+        <v>-0.2111139867637816</v>
       </c>
       <c r="AB2">
-        <v>0.08692067276276166</v>
+        <v>0.1672712264525083</v>
       </c>
       <c r="AC2">
-        <v>-0.1758629804550693</v>
+        <v>-0.3783852132162899</v>
       </c>
       <c r="AD2">
-        <v>51.2</v>
+        <v>25.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>51.2</v>
+        <v>25.1</v>
       </c>
       <c r="AG2">
-        <v>49.34</v>
+        <v>17.86</v>
       </c>
       <c r="AH2">
-        <v>0.4658780709736124</v>
+        <v>0.7110481586402267</v>
       </c>
       <c r="AI2">
-        <v>0.5039370078740159</v>
+        <v>0.9460987561251414</v>
       </c>
       <c r="AJ2">
-        <v>0.4566827101073677</v>
+        <v>0.6364932287954383</v>
       </c>
       <c r="AK2">
-        <v>0.4946861840786044</v>
+        <v>0.9258683255572836</v>
       </c>
       <c r="AL2">
-        <v>5.25</v>
+        <v>2.2</v>
       </c>
       <c r="AM2">
-        <v>5.25</v>
+        <v>2.2</v>
       </c>
       <c r="AN2">
-        <v>-25.98984771573604</v>
+        <v>-6.765498652291106</v>
       </c>
       <c r="AO2">
-        <v>-0.9161904761904761</v>
+        <v>-2.595454545454545</v>
       </c>
       <c r="AP2">
-        <v>-25.04568527918782</v>
+        <v>-4.814016172506738</v>
       </c>
       <c r="AQ2">
-        <v>-0.9161904761904761</v>
+        <v>-2.595454545454545</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Union Investment Corp. P.L.C. (ASE:UINV)</t>
+          <t>Union Tobacco &amp; Cigarette Industries Co. (ASE:UTOB)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,34 +716,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.187</v>
+        <v>-0.221</v>
       </c>
       <c r="G3">
-        <v>-0.3459016393442623</v>
+        <v>-1.053608247422681</v>
       </c>
       <c r="H3">
-        <v>-0.3459016393442623</v>
+        <v>-1.053608247422681</v>
       </c>
       <c r="I3">
-        <v>-0.3942622950819672</v>
+        <v>-1.177319587628866</v>
       </c>
       <c r="J3">
-        <v>-0.3942622950819672</v>
+        <v>-1.177319587628866</v>
       </c>
       <c r="K3">
-        <v>-7.24</v>
+        <v>-0.995</v>
       </c>
       <c r="L3">
-        <v>-0.5934426229508197</v>
+        <v>-0.2051546391752578</v>
       </c>
       <c r="M3">
-        <v>6.51</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.1109028960817717</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.899171270718232</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,79 +755,76 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>6.51</v>
-      </c>
-      <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>1.86</v>
+        <v>7.24</v>
       </c>
       <c r="V3">
-        <v>0.03168654173764907</v>
+        <v>0.7098039215686275</v>
       </c>
       <c r="W3">
-        <v>-4.641025641025641</v>
+        <v>-0.3579136690647483</v>
       </c>
       <c r="X3">
-        <v>0.1197171494289259</v>
+        <v>0.3547058643832672</v>
       </c>
       <c r="Y3">
-        <v>-4.760742790454567</v>
+        <v>-0.7126195334480154</v>
       </c>
       <c r="Z3">
-        <v>0.2255917159763313</v>
+        <v>0.1793174843790439</v>
       </c>
       <c r="AA3">
-        <v>-0.08894230769230768</v>
+        <v>-0.2111139867637816</v>
       </c>
       <c r="AB3">
-        <v>0.08692067276276166</v>
+        <v>0.1672712264525083</v>
       </c>
       <c r="AC3">
-        <v>-0.1758629804550693</v>
+        <v>-0.3783852132162899</v>
       </c>
       <c r="AD3">
-        <v>51.2</v>
+        <v>25.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>51.2</v>
+        <v>25.1</v>
       </c>
       <c r="AG3">
-        <v>49.34</v>
+        <v>17.86</v>
       </c>
       <c r="AH3">
-        <v>0.4658780709736124</v>
+        <v>0.7110481586402267</v>
       </c>
       <c r="AI3">
-        <v>0.5039370078740159</v>
+        <v>0.9460987561251414</v>
       </c>
       <c r="AJ3">
-        <v>0.4566827101073677</v>
+        <v>0.6364932287954383</v>
       </c>
       <c r="AK3">
-        <v>0.4946861840786044</v>
+        <v>0.9258683255572836</v>
       </c>
       <c r="AL3">
-        <v>5.25</v>
+        <v>2.2</v>
       </c>
       <c r="AM3">
-        <v>5.25</v>
+        <v>2.2</v>
       </c>
       <c r="AN3">
-        <v>-25.98984771573604</v>
+        <v>-6.765498652291106</v>
       </c>
       <c r="AO3">
-        <v>-0.9161904761904761</v>
+        <v>-2.595454545454545</v>
       </c>
       <c r="AP3">
-        <v>-25.04568527918782</v>
+        <v>-4.814016172506738</v>
       </c>
       <c r="AQ3">
-        <v>-0.9161904761904761</v>
+        <v>-2.595454545454545</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/jordan/jordan_tobacco.xlsx
+++ b/research/traditional_assets/database/data/jordan/jordan_tobacco.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="ase_utob" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,25 +590,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.221</v>
+        <v>-0.144</v>
       </c>
       <c r="G2">
-        <v>-1.053608247422681</v>
+        <v>-0.4838859416445624</v>
       </c>
       <c r="H2">
-        <v>-1.053608247422681</v>
+        <v>-0.4838859416445624</v>
       </c>
       <c r="I2">
-        <v>-1.177319587628866</v>
+        <v>-0.1704244031830238</v>
       </c>
       <c r="J2">
-        <v>-1.177319587628866</v>
+        <v>-0.1704244031830238</v>
       </c>
       <c r="K2">
-        <v>-0.995</v>
+        <v>-4.82</v>
       </c>
       <c r="L2">
-        <v>-0.2051546391752578</v>
+        <v>-0.3196286472148541</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +632,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>7.24</v>
+        <v>12.77</v>
       </c>
       <c r="V2">
-        <v>0.7098039215686275</v>
+        <v>0.4449477351916376</v>
       </c>
       <c r="W2">
-        <v>-0.3579136690647483</v>
+        <v>0.4672731726871854</v>
       </c>
       <c r="X2">
-        <v>0.3547058643832672</v>
+        <v>0.2148979965422026</v>
       </c>
       <c r="Y2">
-        <v>-0.7126195334480154</v>
+        <v>0.2523751761449828</v>
       </c>
       <c r="Z2">
-        <v>0.1793174843790439</v>
+        <v>0.2989098116947473</v>
       </c>
       <c r="AA2">
-        <v>-0.2111139867637816</v>
+        <v>-0.03037741957594741</v>
       </c>
       <c r="AB2">
-        <v>0.1672712264525083</v>
+        <v>0.1220202691736448</v>
       </c>
       <c r="AC2">
-        <v>-0.3783852132162899</v>
+        <v>-0.1523976887495922</v>
       </c>
       <c r="AD2">
-        <v>25.1</v>
+        <v>60.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>25.1</v>
+        <v>60.8</v>
       </c>
       <c r="AG2">
-        <v>17.86</v>
+        <v>48.03</v>
       </c>
       <c r="AH2">
-        <v>0.7110481586402267</v>
+        <v>0.6793296089385474</v>
       </c>
       <c r="AI2">
-        <v>0.9460987561251414</v>
+        <v>0.5152542372881356</v>
       </c>
       <c r="AJ2">
-        <v>0.6364932287954383</v>
+        <v>0.62596116251792</v>
       </c>
       <c r="AK2">
-        <v>0.9258683255572836</v>
+        <v>0.4564287750641452</v>
       </c>
       <c r="AL2">
-        <v>2.2</v>
+        <v>2.187</v>
       </c>
       <c r="AM2">
-        <v>2.2</v>
+        <v>2.187</v>
       </c>
       <c r="AN2">
-        <v>-6.765498652291106</v>
+        <v>42.81690140845071</v>
       </c>
       <c r="AO2">
-        <v>-2.595454545454545</v>
+        <v>-1.175125743026978</v>
       </c>
       <c r="AP2">
-        <v>-4.814016172506738</v>
+        <v>33.82394366197184</v>
       </c>
       <c r="AQ2">
-        <v>-2.595454545454545</v>
+        <v>-1.175125743026978</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.221</v>
+        <v>-0.144</v>
       </c>
       <c r="G3">
-        <v>-1.053608247422681</v>
+        <v>-0.07519893899204243</v>
       </c>
       <c r="H3">
-        <v>-1.053608247422681</v>
+        <v>-0.07519893899204243</v>
       </c>
       <c r="I3">
-        <v>-1.177319587628866</v>
+        <v>0.1458885941644562</v>
       </c>
       <c r="J3">
-        <v>-1.177319587628866</v>
+        <v>0.1458885941644562</v>
       </c>
       <c r="K3">
-        <v>-0.995</v>
+        <v>-0.59</v>
       </c>
       <c r="L3">
-        <v>-0.2051546391752578</v>
+        <v>-0.07824933687002653</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +760,8973 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>7.24</v>
+        <v>3.37</v>
       </c>
       <c r="V3">
-        <v>0.7098039215686275</v>
+        <v>0.3008928571428572</v>
       </c>
       <c r="W3">
-        <v>-0.3579136690647483</v>
+        <v>-0.4125874125874126</v>
       </c>
       <c r="X3">
-        <v>0.3547058643832672</v>
+        <v>0.2520335819397216</v>
       </c>
       <c r="Y3">
-        <v>-0.7126195334480154</v>
+        <v>-0.6646209945271342</v>
       </c>
       <c r="Z3">
-        <v>0.1793174843790439</v>
+        <v>0.3908761016070503</v>
       </c>
       <c r="AA3">
-        <v>-0.2111139867637816</v>
+        <v>0.05702436495593573</v>
       </c>
       <c r="AB3">
-        <v>0.1672712264525083</v>
+        <v>0.1242647870414119</v>
       </c>
       <c r="AC3">
-        <v>-0.3783852132162899</v>
+        <v>-0.06724042208547622</v>
       </c>
       <c r="AD3">
-        <v>25.1</v>
+        <v>33.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>25.1</v>
+        <v>33.9</v>
       </c>
       <c r="AG3">
-        <v>17.86</v>
+        <v>30.53</v>
       </c>
       <c r="AH3">
-        <v>0.7110481586402267</v>
+        <v>0.7516629711751663</v>
       </c>
       <c r="AI3">
-        <v>0.9460987561251414</v>
+        <v>0.5957820738137083</v>
       </c>
       <c r="AJ3">
-        <v>0.6364932287954383</v>
+        <v>0.7316079559070213</v>
       </c>
       <c r="AK3">
-        <v>0.9258683255572836</v>
+        <v>0.570334391929759</v>
       </c>
       <c r="AL3">
-        <v>2.2</v>
+        <v>1.49</v>
       </c>
       <c r="AM3">
-        <v>2.2</v>
+        <v>1.49</v>
       </c>
       <c r="AN3">
-        <v>-6.765498652291106</v>
+        <v>11.18811881188119</v>
       </c>
       <c r="AO3">
-        <v>-2.595454545454545</v>
+        <v>0.738255033557047</v>
       </c>
       <c r="AP3">
-        <v>-4.814016172506738</v>
+        <v>10.07590759075908</v>
       </c>
       <c r="AQ3">
-        <v>-2.595454545454545</v>
+        <v>0.738255033557047</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Union Investment Corp. P.L.C. (ASE:UINV)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Tobacco</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>-0.144</v>
+      </c>
+      <c r="G4">
+        <v>-0.8925729442970822</v>
+      </c>
+      <c r="H4">
+        <v>-0.8925729442970822</v>
+      </c>
+      <c r="I4">
+        <v>-0.486737400530504</v>
+      </c>
+      <c r="J4">
+        <v>-0.486737400530504</v>
+      </c>
+      <c r="K4">
+        <v>-4.23</v>
+      </c>
+      <c r="L4">
+        <v>-0.5610079575596818</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>9.4</v>
+      </c>
+      <c r="V4">
+        <v>0.5371428571428571</v>
+      </c>
+      <c r="W4">
+        <v>1.347133757961783</v>
+      </c>
+      <c r="X4">
+        <v>0.1777624111446837</v>
+      </c>
+      <c r="Y4">
+        <v>1.1693713468171</v>
+      </c>
+      <c r="Z4">
+        <v>0.241976893453145</v>
+      </c>
+      <c r="AA4">
+        <v>-0.1177792041078305</v>
+      </c>
+      <c r="AB4">
+        <v>0.1197757513058777</v>
+      </c>
+      <c r="AC4">
+        <v>-0.2375549554137082</v>
+      </c>
+      <c r="AD4">
+        <v>26.9</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>26.9</v>
+      </c>
+      <c r="AG4">
+        <v>17.5</v>
+      </c>
+      <c r="AH4">
+        <v>0.6058558558558559</v>
+      </c>
+      <c r="AI4">
+        <v>0.4402618657937806</v>
+      </c>
+      <c r="AJ4">
+        <v>0.5</v>
+      </c>
+      <c r="AK4">
+        <v>0.3384912959381045</v>
+      </c>
+      <c r="AL4">
+        <v>0.697</v>
+      </c>
+      <c r="AM4">
+        <v>0.697</v>
+      </c>
+      <c r="AN4">
+        <v>-16.70807453416149</v>
+      </c>
+      <c r="AO4">
+        <v>-5.265423242467719</v>
+      </c>
+      <c r="AP4">
+        <v>-10.8695652173913</v>
+      </c>
+      <c r="AQ4">
+        <v>-5.265423242467719</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Union Tobacco &amp; Cigarette Industries Co. (ASE:UTOB)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ASE:UTOB</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Tobacco</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1.98456375838926</v>
+      </c>
+      <c r="F2">
+        <v>4.51681267125227</v>
+      </c>
+      <c r="G2">
+        <v>11.1881188118812</v>
+      </c>
+      <c r="H2">
+        <v>7.14455445544554</v>
+      </c>
+      <c r="I2">
+        <v>0.751662971175166</v>
+      </c>
+      <c r="J2">
+        <v>0.48</v>
+      </c>
+      <c r="K2">
+        <v>11.2</v>
+      </c>
+      <c r="L2">
+        <v>44.0054130866176</v>
+      </c>
+      <c r="M2">
+        <v>41.73</v>
+      </c>
+      <c r="N2">
+        <v>62.2834130866176</v>
+      </c>
+      <c r="O2">
+        <v>33.9</v>
+      </c>
+      <c r="P2">
+        <v>21.648</v>
+      </c>
+      <c r="Q2">
+        <v>0.124264787041412</v>
+      </c>
+      <c r="R2">
+        <v>0.0960615626937185</v>
+      </c>
+      <c r="S2">
+        <v>0.08205208784197041</v>
+      </c>
+      <c r="T2">
+        <v>0.04072</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.252033581939722</v>
+      </c>
+      <c r="X2">
+        <v>0.147146082103305</v>
+      </c>
+      <c r="Y2">
+        <v>1.90668486710818</v>
+      </c>
+      <c r="Z2">
+        <v>0.968805350815849</v>
+      </c>
+      <c r="AA2">
+        <v>33.9</v>
+      </c>
+      <c r="AB2">
+        <v>0.102565109802463</v>
+      </c>
+      <c r="AC2">
+        <v>1.984563758389262</v>
+      </c>
+      <c r="AD2">
+        <v>33.9</v>
+      </c>
+      <c r="AE2">
+        <v>1.49</v>
+      </c>
+      <c r="AF2">
+        <v>0.073</v>
+      </c>
+      <c r="AG2">
+        <v>3.03</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>11.2</v>
+      </c>
+      <c r="AK2">
+        <v>0.1118347271844283</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.2</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>0.2010000000000005</v>
+      </c>
+      <c r="AR2">
+        <v>1.49</v>
+      </c>
+      <c r="AS2">
+        <v>33.9</v>
+      </c>
+      <c r="AT2">
+        <v>3.37</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.101122967581547</v>
+      </c>
+      <c r="C2">
+        <v>60.59522051876901</v>
+      </c>
+      <c r="D2">
+        <v>57.22522051876901</v>
+      </c>
+      <c r="E2">
+        <v>-33.9</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>3.37</v>
+      </c>
+      <c r="H2">
+        <v>11.2</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>5.05</v>
+      </c>
+      <c r="K2">
+        <v>0.073</v>
+      </c>
+      <c r="L2">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="O2">
+        <v>0.9954</v>
+      </c>
+      <c r="P2">
+        <v>3.981599999999999</v>
+      </c>
+      <c r="Q2">
+        <v>4.0546</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.101122967581547</v>
+      </c>
+      <c r="T2">
+        <v>0.5572774141861078</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.2</v>
+      </c>
+      <c r="W2">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1009679216463839</v>
+      </c>
+      <c r="C3">
+        <v>60.28693942580783</v>
+      </c>
+      <c r="D3">
+        <v>57.36793942580783</v>
+      </c>
+      <c r="E3">
+        <v>-33.449</v>
+      </c>
+      <c r="F3">
+        <v>0.451</v>
+      </c>
+      <c r="G3">
+        <v>3.37</v>
+      </c>
+      <c r="H3">
+        <v>11.2</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>5.05</v>
+      </c>
+      <c r="K3">
+        <v>0.073</v>
+      </c>
+      <c r="L3">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M3">
+        <v>0.0201597</v>
+      </c>
+      <c r="N3">
+        <v>4.9568403</v>
+      </c>
+      <c r="O3">
+        <v>0.99136806</v>
+      </c>
+      <c r="P3">
+        <v>3.96547224</v>
+      </c>
+      <c r="Q3">
+        <v>4.03847224</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1016265875215999</v>
+      </c>
+      <c r="T3">
+        <v>0.5617806660179148</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.2</v>
+      </c>
+      <c r="W3">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>246.8786737897885</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1008128757112208</v>
+      </c>
+      <c r="C4">
+        <v>59.9793719906525</v>
+      </c>
+      <c r="D4">
+        <v>57.51137199065251</v>
+      </c>
+      <c r="E4">
+        <v>-32.998</v>
+      </c>
+      <c r="F4">
+        <v>0.9019999999999999</v>
+      </c>
+      <c r="G4">
+        <v>3.37</v>
+      </c>
+      <c r="H4">
+        <v>11.2</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>5.05</v>
+      </c>
+      <c r="K4">
+        <v>0.073</v>
+      </c>
+      <c r="L4">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M4">
+        <v>0.0403194</v>
+      </c>
+      <c r="N4">
+        <v>4.9366806</v>
+      </c>
+      <c r="O4">
+        <v>0.98733612</v>
+      </c>
+      <c r="P4">
+        <v>3.94934448</v>
+      </c>
+      <c r="Q4">
+        <v>4.02234448</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1021404854196131</v>
+      </c>
+      <c r="T4">
+        <v>0.5663758209483299</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.2</v>
+      </c>
+      <c r="W4">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>123.4393368948943</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1006578297760577</v>
+      </c>
+      <c r="C5">
+        <v>59.67252357962814</v>
+      </c>
+      <c r="D5">
+        <v>57.65552357962815</v>
+      </c>
+      <c r="E5">
+        <v>-32.547</v>
+      </c>
+      <c r="F5">
+        <v>1.353</v>
+      </c>
+      <c r="G5">
+        <v>3.37</v>
+      </c>
+      <c r="H5">
+        <v>11.2</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>5.05</v>
+      </c>
+      <c r="K5">
+        <v>0.073</v>
+      </c>
+      <c r="L5">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M5">
+        <v>0.06047909999999999</v>
+      </c>
+      <c r="N5">
+        <v>4.916520899999999</v>
+      </c>
+      <c r="O5">
+        <v>0.9833041799999999</v>
+      </c>
+      <c r="P5">
+        <v>3.933216719999999</v>
+      </c>
+      <c r="Q5">
+        <v>4.006216719999999</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.102664979150575</v>
+      </c>
+      <c r="T5">
+        <v>0.5710657213412279</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.2</v>
+      </c>
+      <c r="W5">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>82.29289126326285</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1005027838408946</v>
+      </c>
+      <c r="C6">
+        <v>59.36639961299759</v>
+      </c>
+      <c r="D6">
+        <v>57.80039961299759</v>
+      </c>
+      <c r="E6">
+        <v>-32.096</v>
+      </c>
+      <c r="F6">
+        <v>1.804</v>
+      </c>
+      <c r="G6">
+        <v>3.37</v>
+      </c>
+      <c r="H6">
+        <v>11.2</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>5.05</v>
+      </c>
+      <c r="K6">
+        <v>0.073</v>
+      </c>
+      <c r="L6">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M6">
+        <v>0.0806388</v>
+      </c>
+      <c r="N6">
+        <v>4.896361199999999</v>
+      </c>
+      <c r="O6">
+        <v>0.9792722399999999</v>
+      </c>
+      <c r="P6">
+        <v>3.91708896</v>
+      </c>
+      <c r="Q6">
+        <v>3.99008896</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1032003998342652</v>
+      </c>
+      <c r="T6">
+        <v>0.5758533279923114</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.2</v>
+      </c>
+      <c r="W6">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>61.71966844744713</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1003477379057315</v>
+      </c>
+      <c r="C7">
+        <v>59.0610055656408</v>
+      </c>
+      <c r="D7">
+        <v>57.9460055656408</v>
+      </c>
+      <c r="E7">
+        <v>-31.645</v>
+      </c>
+      <c r="F7">
+        <v>2.255</v>
+      </c>
+      <c r="G7">
+        <v>3.37</v>
+      </c>
+      <c r="H7">
+        <v>11.2</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>5.05</v>
+      </c>
+      <c r="K7">
+        <v>0.073</v>
+      </c>
+      <c r="L7">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M7">
+        <v>0.1007985</v>
+      </c>
+      <c r="N7">
+        <v>4.8762015</v>
+      </c>
+      <c r="O7">
+        <v>0.9752402999999999</v>
+      </c>
+      <c r="P7">
+        <v>3.9009612</v>
+      </c>
+      <c r="Q7">
+        <v>3.9739612</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.103747092532349</v>
+      </c>
+      <c r="T7">
+        <v>0.5807417263623649</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.2</v>
+      </c>
+      <c r="W7">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>49.3757347579577</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1001926919705684</v>
+      </c>
+      <c r="C8">
+        <v>58.75634696774443</v>
+      </c>
+      <c r="D8">
+        <v>58.09234696774444</v>
+      </c>
+      <c r="E8">
+        <v>-31.194</v>
+      </c>
+      <c r="F8">
+        <v>2.706</v>
+      </c>
+      <c r="G8">
+        <v>3.37</v>
+      </c>
+      <c r="H8">
+        <v>11.2</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>5.05</v>
+      </c>
+      <c r="K8">
+        <v>0.073</v>
+      </c>
+      <c r="L8">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M8">
+        <v>0.1209582</v>
+      </c>
+      <c r="N8">
+        <v>4.8560418</v>
+      </c>
+      <c r="O8">
+        <v>0.97120836</v>
+      </c>
+      <c r="P8">
+        <v>3.88483344</v>
+      </c>
+      <c r="Q8">
+        <v>3.95783344</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1043054169899664</v>
+      </c>
+      <c r="T8">
+        <v>0.5857341332083772</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.2</v>
+      </c>
+      <c r="W8">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>41.14644563163142</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1000376460354053</v>
+      </c>
+      <c r="C9">
+        <v>58.45242940550219</v>
+      </c>
+      <c r="D9">
+        <v>58.23942940550219</v>
+      </c>
+      <c r="E9">
+        <v>-30.743</v>
+      </c>
+      <c r="F9">
+        <v>3.157</v>
+      </c>
+      <c r="G9">
+        <v>3.37</v>
+      </c>
+      <c r="H9">
+        <v>11.2</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>5.05</v>
+      </c>
+      <c r="K9">
+        <v>0.073</v>
+      </c>
+      <c r="L9">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M9">
+        <v>0.1411179</v>
+      </c>
+      <c r="N9">
+        <v>4.835882099999999</v>
+      </c>
+      <c r="O9">
+        <v>0.9671764199999999</v>
+      </c>
+      <c r="P9">
+        <v>3.868705679999999</v>
+      </c>
+      <c r="Q9">
+        <v>3.941705679999999</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.104875748425167</v>
+      </c>
+      <c r="T9">
+        <v>0.5908339036424756</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.2</v>
+      </c>
+      <c r="W9">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>35.26838196996978</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.09988260010024226</v>
+      </c>
+      <c r="C10">
+        <v>58.14925852182536</v>
+      </c>
+      <c r="D10">
+        <v>58.38725852182536</v>
+      </c>
+      <c r="E10">
+        <v>-30.292</v>
+      </c>
+      <c r="F10">
+        <v>3.608</v>
+      </c>
+      <c r="G10">
+        <v>3.37</v>
+      </c>
+      <c r="H10">
+        <v>11.2</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>5.05</v>
+      </c>
+      <c r="K10">
+        <v>0.073</v>
+      </c>
+      <c r="L10">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M10">
+        <v>0.1612776</v>
+      </c>
+      <c r="N10">
+        <v>4.815722399999999</v>
+      </c>
+      <c r="O10">
+        <v>0.96314448</v>
+      </c>
+      <c r="P10">
+        <v>3.852577919999999</v>
+      </c>
+      <c r="Q10">
+        <v>3.925577919999999</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1054584783698285</v>
+      </c>
+      <c r="T10">
+        <v>0.5960445386512283</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.2</v>
+      </c>
+      <c r="W10">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>30.85983422372356</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.09972755416507915</v>
+      </c>
+      <c r="C11">
+        <v>57.84684001706474</v>
+      </c>
+      <c r="D11">
+        <v>58.53584001706474</v>
+      </c>
+      <c r="E11">
+        <v>-29.841</v>
+      </c>
+      <c r="F11">
+        <v>4.058999999999999</v>
+      </c>
+      <c r="G11">
+        <v>3.37</v>
+      </c>
+      <c r="H11">
+        <v>11.2</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>5.05</v>
+      </c>
+      <c r="K11">
+        <v>0.073</v>
+      </c>
+      <c r="L11">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M11">
+        <v>0.1814373</v>
+      </c>
+      <c r="N11">
+        <v>4.7955627</v>
+      </c>
+      <c r="O11">
+        <v>0.95911254</v>
+      </c>
+      <c r="P11">
+        <v>3.83645016</v>
+      </c>
+      <c r="Q11">
+        <v>3.90945016</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1060540155660211</v>
+      </c>
+      <c r="T11">
+        <v>0.6013696931107229</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.2</v>
+      </c>
+      <c r="W11">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>27.43096375442095</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.09957250822991608</v>
+      </c>
+      <c r="C12">
+        <v>57.54517964974317</v>
+      </c>
+      <c r="D12">
+        <v>58.68517964974317</v>
+      </c>
+      <c r="E12">
+        <v>-29.39</v>
+      </c>
+      <c r="F12">
+        <v>4.51</v>
+      </c>
+      <c r="G12">
+        <v>3.37</v>
+      </c>
+      <c r="H12">
+        <v>11.2</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>5.05</v>
+      </c>
+      <c r="K12">
+        <v>0.073</v>
+      </c>
+      <c r="L12">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M12">
+        <v>0.201597</v>
+      </c>
+      <c r="N12">
+        <v>4.775403</v>
+      </c>
+      <c r="O12">
+        <v>0.9550806000000001</v>
+      </c>
+      <c r="P12">
+        <v>3.8203224</v>
+      </c>
+      <c r="Q12">
+        <v>3.8933224</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.106662786922129</v>
+      </c>
+      <c r="T12">
+        <v>0.6068131843359841</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.2</v>
+      </c>
+      <c r="W12">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>24.68786737897885</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.09941746229475297</v>
+      </c>
+      <c r="C13">
+        <v>57.24428323729961</v>
+      </c>
+      <c r="D13">
+        <v>58.83528323729961</v>
+      </c>
+      <c r="E13">
+        <v>-28.939</v>
+      </c>
+      <c r="F13">
+        <v>4.960999999999999</v>
+      </c>
+      <c r="G13">
+        <v>3.37</v>
+      </c>
+      <c r="H13">
+        <v>11.2</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>5.05</v>
+      </c>
+      <c r="K13">
+        <v>0.073</v>
+      </c>
+      <c r="L13">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M13">
+        <v>0.2217567</v>
+      </c>
+      <c r="N13">
+        <v>4.755243299999999</v>
+      </c>
+      <c r="O13">
+        <v>0.9510486599999999</v>
+      </c>
+      <c r="P13">
+        <v>3.80419464</v>
+      </c>
+      <c r="Q13">
+        <v>3.877194639999999</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1072852385334303</v>
+      </c>
+      <c r="T13">
+        <v>0.6123790012067566</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.2</v>
+      </c>
+      <c r="W13">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>22.44351579907168</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.09926241635958988</v>
+      </c>
+      <c r="C14">
+        <v>56.9441566568444</v>
+      </c>
+      <c r="D14">
+        <v>58.9861566568444</v>
+      </c>
+      <c r="E14">
+        <v>-28.488</v>
+      </c>
+      <c r="F14">
+        <v>5.411999999999999</v>
+      </c>
+      <c r="G14">
+        <v>3.37</v>
+      </c>
+      <c r="H14">
+        <v>11.2</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>5.05</v>
+      </c>
+      <c r="K14">
+        <v>0.073</v>
+      </c>
+      <c r="L14">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M14">
+        <v>0.2419164</v>
+      </c>
+      <c r="N14">
+        <v>4.735083599999999</v>
+      </c>
+      <c r="O14">
+        <v>0.9470167199999999</v>
+      </c>
+      <c r="P14">
+        <v>3.78806688</v>
+      </c>
+      <c r="Q14">
+        <v>3.86106688</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1079218367722612</v>
+      </c>
+      <c r="T14">
+        <v>0.6180713139155014</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.2</v>
+      </c>
+      <c r="W14">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>20.57322281581571</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.09910737042442677</v>
+      </c>
+      <c r="C15">
+        <v>56.6448058459265</v>
+      </c>
+      <c r="D15">
+        <v>59.1378058459265</v>
+      </c>
+      <c r="E15">
+        <v>-28.037</v>
+      </c>
+      <c r="F15">
+        <v>5.863</v>
+      </c>
+      <c r="G15">
+        <v>3.37</v>
+      </c>
+      <c r="H15">
+        <v>11.2</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>5.05</v>
+      </c>
+      <c r="K15">
+        <v>0.073</v>
+      </c>
+      <c r="L15">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M15">
+        <v>0.2620761</v>
+      </c>
+      <c r="N15">
+        <v>4.7149239</v>
+      </c>
+      <c r="O15">
+        <v>0.94298478</v>
+      </c>
+      <c r="P15">
+        <v>3.77193912</v>
+      </c>
+      <c r="Q15">
+        <v>3.84493912</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1085730694533641</v>
+      </c>
+      <c r="T15">
+        <v>0.6238944843876655</v>
+      </c>
+      <c r="U15">
+        <v>0.0447</v>
+      </c>
+      <c r="V15">
+        <v>0.2</v>
+      </c>
+      <c r="W15">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>18.99066721459912</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.09895232448926369</v>
+      </c>
+      <c r="C16">
+        <v>56.3462368033122</v>
+      </c>
+      <c r="D16">
+        <v>59.2902368033122</v>
+      </c>
+      <c r="E16">
+        <v>-27.586</v>
+      </c>
+      <c r="F16">
+        <v>6.314</v>
+      </c>
+      <c r="G16">
+        <v>3.37</v>
+      </c>
+      <c r="H16">
+        <v>11.2</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>5.05</v>
+      </c>
+      <c r="K16">
+        <v>0.073</v>
+      </c>
+      <c r="L16">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M16">
+        <v>0.2822358</v>
+      </c>
+      <c r="N16">
+        <v>4.6947642</v>
+      </c>
+      <c r="O16">
+        <v>0.93895284</v>
+      </c>
+      <c r="P16">
+        <v>3.75581136</v>
+      </c>
+      <c r="Q16">
+        <v>3.82881136</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1092394470805392</v>
+      </c>
+      <c r="T16">
+        <v>0.6298530774289497</v>
+      </c>
+      <c r="U16">
+        <v>0.0447</v>
+      </c>
+      <c r="V16">
+        <v>0.2</v>
+      </c>
+      <c r="W16">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>17.63419098498489</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.09879727855410061</v>
+      </c>
+      <c r="C17">
+        <v>56.04845558977634</v>
+      </c>
+      <c r="D17">
+        <v>59.44345558977634</v>
+      </c>
+      <c r="E17">
+        <v>-27.135</v>
+      </c>
+      <c r="F17">
+        <v>6.764999999999999</v>
+      </c>
+      <c r="G17">
+        <v>3.37</v>
+      </c>
+      <c r="H17">
+        <v>11.2</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>5.05</v>
+      </c>
+      <c r="K17">
+        <v>0.073</v>
+      </c>
+      <c r="L17">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M17">
+        <v>0.3023955</v>
+      </c>
+      <c r="N17">
+        <v>4.674604499999999</v>
+      </c>
+      <c r="O17">
+        <v>0.9349208999999998</v>
+      </c>
+      <c r="P17">
+        <v>3.739683599999999</v>
+      </c>
+      <c r="Q17">
+        <v>3.812683599999999</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1099215041812948</v>
+      </c>
+      <c r="T17">
+        <v>0.6359518726594406</v>
+      </c>
+      <c r="U17">
+        <v>0.0447</v>
+      </c>
+      <c r="V17">
+        <v>0.2</v>
+      </c>
+      <c r="W17">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>16.45857825265256</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.09864223261893749</v>
+      </c>
+      <c r="C18">
+        <v>55.75146832890545</v>
+      </c>
+      <c r="D18">
+        <v>59.59746832890545</v>
+      </c>
+      <c r="E18">
+        <v>-26.684</v>
+      </c>
+      <c r="F18">
+        <v>7.215999999999999</v>
+      </c>
+      <c r="G18">
+        <v>3.37</v>
+      </c>
+      <c r="H18">
+        <v>11.2</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>5.05</v>
+      </c>
+      <c r="K18">
+        <v>0.073</v>
+      </c>
+      <c r="L18">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M18">
+        <v>0.3225552</v>
+      </c>
+      <c r="N18">
+        <v>4.654444799999999</v>
+      </c>
+      <c r="O18">
+        <v>0.9308889599999999</v>
+      </c>
+      <c r="P18">
+        <v>3.72355584</v>
+      </c>
+      <c r="Q18">
+        <v>3.796555839999999</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1106198007368304</v>
+      </c>
+      <c r="T18">
+        <v>0.6421958773001812</v>
+      </c>
+      <c r="U18">
+        <v>0.0447</v>
+      </c>
+      <c r="V18">
+        <v>0.2</v>
+      </c>
+      <c r="W18">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>15.42991711186178</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.0984871866837744</v>
+      </c>
+      <c r="C19">
+        <v>55.45528120791354</v>
+      </c>
+      <c r="D19">
+        <v>59.75228120791354</v>
+      </c>
+      <c r="E19">
+        <v>-26.233</v>
+      </c>
+      <c r="F19">
+        <v>7.667</v>
+      </c>
+      <c r="G19">
+        <v>3.37</v>
+      </c>
+      <c r="H19">
+        <v>11.2</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>5.05</v>
+      </c>
+      <c r="K19">
+        <v>0.073</v>
+      </c>
+      <c r="L19">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M19">
+        <v>0.3427149</v>
+      </c>
+      <c r="N19">
+        <v>4.6342851</v>
+      </c>
+      <c r="O19">
+        <v>0.9268570199999999</v>
+      </c>
+      <c r="P19">
+        <v>3.70742808</v>
+      </c>
+      <c r="Q19">
+        <v>3.78042808</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1113349237153908</v>
+      </c>
+      <c r="T19">
+        <v>0.6485903398840723</v>
+      </c>
+      <c r="U19">
+        <v>0.0447</v>
+      </c>
+      <c r="V19">
+        <v>0.2</v>
+      </c>
+      <c r="W19">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>14.52227492881109</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.09833214074861132</v>
+      </c>
+      <c r="C20">
+        <v>55.15990047847075</v>
+      </c>
+      <c r="D20">
+        <v>59.90790047847074</v>
+      </c>
+      <c r="E20">
+        <v>-25.782</v>
+      </c>
+      <c r="F20">
+        <v>8.117999999999999</v>
+      </c>
+      <c r="G20">
+        <v>3.37</v>
+      </c>
+      <c r="H20">
+        <v>11.2</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>5.05</v>
+      </c>
+      <c r="K20">
+        <v>0.073</v>
+      </c>
+      <c r="L20">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M20">
+        <v>0.3628746</v>
+      </c>
+      <c r="N20">
+        <v>4.6141254</v>
+      </c>
+      <c r="O20">
+        <v>0.92282508</v>
+      </c>
+      <c r="P20">
+        <v>3.69130032</v>
+      </c>
+      <c r="Q20">
+        <v>3.76430032</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1120674887178187</v>
+      </c>
+      <c r="T20">
+        <v>0.6551407649700096</v>
+      </c>
+      <c r="U20">
+        <v>0.0447</v>
+      </c>
+      <c r="V20">
+        <v>0.2</v>
+      </c>
+      <c r="W20">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>13.71548187721047</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.09817709481344823</v>
+      </c>
+      <c r="C21">
+        <v>54.86533245754491</v>
+      </c>
+      <c r="D21">
+        <v>60.06433245754491</v>
+      </c>
+      <c r="E21">
+        <v>-25.331</v>
+      </c>
+      <c r="F21">
+        <v>8.568999999999999</v>
+      </c>
+      <c r="G21">
+        <v>3.37</v>
+      </c>
+      <c r="H21">
+        <v>11.2</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>5.05</v>
+      </c>
+      <c r="K21">
+        <v>0.073</v>
+      </c>
+      <c r="L21">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M21">
+        <v>0.3830343</v>
+      </c>
+      <c r="N21">
+        <v>4.593965699999999</v>
+      </c>
+      <c r="O21">
+        <v>0.9187931399999999</v>
+      </c>
+      <c r="P21">
+        <v>3.675172559999999</v>
+      </c>
+      <c r="Q21">
+        <v>3.748172559999999</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1128181417449978</v>
+      </c>
+      <c r="T21">
+        <v>0.6618529289469577</v>
+      </c>
+      <c r="U21">
+        <v>0.0447</v>
+      </c>
+      <c r="V21">
+        <v>0.2</v>
+      </c>
+      <c r="W21">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>12.99361440998887</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.09819804887828514</v>
+      </c>
+      <c r="C22">
+        <v>54.39314334543654</v>
+      </c>
+      <c r="D22">
+        <v>60.04314334543654</v>
+      </c>
+      <c r="E22">
+        <v>-24.88</v>
+      </c>
+      <c r="F22">
+        <v>9.02</v>
+      </c>
+      <c r="G22">
+        <v>3.37</v>
+      </c>
+      <c r="H22">
+        <v>11.2</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>5.05</v>
+      </c>
+      <c r="K22">
+        <v>0.073</v>
+      </c>
+      <c r="L22">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M22">
+        <v>0.413116</v>
+      </c>
+      <c r="N22">
+        <v>4.563884</v>
+      </c>
+      <c r="O22">
+        <v>0.9127768000000001</v>
+      </c>
+      <c r="P22">
+        <v>3.6511072</v>
+      </c>
+      <c r="Q22">
+        <v>3.7241072</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1135875610978564</v>
+      </c>
+      <c r="T22">
+        <v>0.6687328970233293</v>
+      </c>
+      <c r="U22">
+        <v>0.0458</v>
+      </c>
+      <c r="V22">
+        <v>0.2</v>
+      </c>
+      <c r="W22">
+        <v>0.03664</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>12.04746366637942</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.09805180294312205</v>
+      </c>
+      <c r="C23">
+        <v>54.09034247546325</v>
+      </c>
+      <c r="D23">
+        <v>60.19134247546325</v>
+      </c>
+      <c r="E23">
+        <v>-24.429</v>
+      </c>
+      <c r="F23">
+        <v>9.470999999999998</v>
+      </c>
+      <c r="G23">
+        <v>3.37</v>
+      </c>
+      <c r="H23">
+        <v>11.2</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>5.05</v>
+      </c>
+      <c r="K23">
+        <v>0.073</v>
+      </c>
+      <c r="L23">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M23">
+        <v>0.4337717999999999</v>
+      </c>
+      <c r="N23">
+        <v>4.5432282</v>
+      </c>
+      <c r="O23">
+        <v>0.90864564</v>
+      </c>
+      <c r="P23">
+        <v>3.63458256</v>
+      </c>
+      <c r="Q23">
+        <v>3.70758256</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1143764594216735</v>
+      </c>
+      <c r="T23">
+        <v>0.6757870415066978</v>
+      </c>
+      <c r="U23">
+        <v>0.0458</v>
+      </c>
+      <c r="V23">
+        <v>0.2</v>
+      </c>
+      <c r="W23">
+        <v>0.03664</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>11.47377492036135</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.09790555700795894</v>
+      </c>
+      <c r="C24">
+        <v>53.78827498899766</v>
+      </c>
+      <c r="D24">
+        <v>60.34027498899766</v>
+      </c>
+      <c r="E24">
+        <v>-23.978</v>
+      </c>
+      <c r="F24">
+        <v>9.921999999999999</v>
+      </c>
+      <c r="G24">
+        <v>3.37</v>
+      </c>
+      <c r="H24">
+        <v>11.2</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>5.05</v>
+      </c>
+      <c r="K24">
+        <v>0.073</v>
+      </c>
+      <c r="L24">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M24">
+        <v>0.4544275999999999</v>
+      </c>
+      <c r="N24">
+        <v>4.5225724</v>
+      </c>
+      <c r="O24">
+        <v>0.90451448</v>
+      </c>
+      <c r="P24">
+        <v>3.61805792</v>
+      </c>
+      <c r="Q24">
+        <v>3.69105792</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1151855859076397</v>
+      </c>
+      <c r="T24">
+        <v>0.6830220614896398</v>
+      </c>
+      <c r="U24">
+        <v>0.0458</v>
+      </c>
+      <c r="V24">
+        <v>0.2</v>
+      </c>
+      <c r="W24">
+        <v>0.03664</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>10.95223969670856</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.09775931107279585</v>
+      </c>
+      <c r="C25">
+        <v>53.48694634341474</v>
+      </c>
+      <c r="D25">
+        <v>60.48994634341474</v>
+      </c>
+      <c r="E25">
+        <v>-23.527</v>
+      </c>
+      <c r="F25">
+        <v>10.373</v>
+      </c>
+      <c r="G25">
+        <v>3.37</v>
+      </c>
+      <c r="H25">
+        <v>11.2</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>5.05</v>
+      </c>
+      <c r="K25">
+        <v>0.073</v>
+      </c>
+      <c r="L25">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M25">
+        <v>0.4750834</v>
+      </c>
+      <c r="N25">
+        <v>4.501916599999999</v>
+      </c>
+      <c r="O25">
+        <v>0.90038332</v>
+      </c>
+      <c r="P25">
+        <v>3.60153328</v>
+      </c>
+      <c r="Q25">
+        <v>3.674533279999999</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1160157286659686</v>
+      </c>
+      <c r="T25">
+        <v>0.6904450040695413</v>
+      </c>
+      <c r="U25">
+        <v>0.0458</v>
+      </c>
+      <c r="V25">
+        <v>0.2</v>
+      </c>
+      <c r="W25">
+        <v>0.03664</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>10.47605536206906</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.09761306513763275</v>
+      </c>
+      <c r="C26">
+        <v>53.1863620503713</v>
+      </c>
+      <c r="D26">
+        <v>60.6403620503713</v>
+      </c>
+      <c r="E26">
+        <v>-23.076</v>
+      </c>
+      <c r="F26">
+        <v>10.824</v>
+      </c>
+      <c r="G26">
+        <v>3.37</v>
+      </c>
+      <c r="H26">
+        <v>11.2</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>5.05</v>
+      </c>
+      <c r="K26">
+        <v>0.073</v>
+      </c>
+      <c r="L26">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M26">
+        <v>0.4957391999999999</v>
+      </c>
+      <c r="N26">
+        <v>4.481260799999999</v>
+      </c>
+      <c r="O26">
+        <v>0.89625216</v>
+      </c>
+      <c r="P26">
+        <v>3.585008639999999</v>
+      </c>
+      <c r="Q26">
+        <v>3.658008639999999</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1168677172863589</v>
+      </c>
+      <c r="T26">
+        <v>0.6980632872436507</v>
+      </c>
+      <c r="U26">
+        <v>0.0458</v>
+      </c>
+      <c r="V26">
+        <v>0.2</v>
+      </c>
+      <c r="W26">
+        <v>0.03664</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>10.03955305531618</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.09790681920246966</v>
+      </c>
+      <c r="C27">
+        <v>52.43398645469833</v>
+      </c>
+      <c r="D27">
+        <v>60.33898645469833</v>
+      </c>
+      <c r="E27">
+        <v>-22.625</v>
+      </c>
+      <c r="F27">
+        <v>11.275</v>
+      </c>
+      <c r="G27">
+        <v>3.37</v>
+      </c>
+      <c r="H27">
+        <v>11.2</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>5.05</v>
+      </c>
+      <c r="K27">
+        <v>0.073</v>
+      </c>
+      <c r="L27">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M27">
+        <v>0.5411999999999999</v>
+      </c>
+      <c r="N27">
+        <v>4.4358</v>
+      </c>
+      <c r="O27">
+        <v>0.8871599999999999</v>
+      </c>
+      <c r="P27">
+        <v>3.54864</v>
+      </c>
+      <c r="Q27">
+        <v>3.62164</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1177424256032929</v>
+      </c>
+      <c r="T27">
+        <v>0.7058847246357365</v>
+      </c>
+      <c r="U27">
+        <v>0.048</v>
+      </c>
+      <c r="V27">
+        <v>0.2</v>
+      </c>
+      <c r="W27">
+        <v>0.0384</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>9.196230598669624</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.09777817326730658</v>
+      </c>
+      <c r="C28">
+        <v>52.11460065889004</v>
+      </c>
+      <c r="D28">
+        <v>60.47060065889004</v>
+      </c>
+      <c r="E28">
+        <v>-22.174</v>
+      </c>
+      <c r="F28">
+        <v>11.726</v>
+      </c>
+      <c r="G28">
+        <v>3.37</v>
+      </c>
+      <c r="H28">
+        <v>11.2</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>5.05</v>
+      </c>
+      <c r="K28">
+        <v>0.073</v>
+      </c>
+      <c r="L28">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M28">
+        <v>0.562848</v>
+      </c>
+      <c r="N28">
+        <v>4.414152</v>
+      </c>
+      <c r="O28">
+        <v>0.8828304</v>
+      </c>
+      <c r="P28">
+        <v>3.5313216</v>
+      </c>
+      <c r="Q28">
+        <v>3.6043216</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1186407746855494</v>
+      </c>
+      <c r="T28">
+        <v>0.7139175522276083</v>
+      </c>
+      <c r="U28">
+        <v>0.048</v>
+      </c>
+      <c r="V28">
+        <v>0.2</v>
+      </c>
+      <c r="W28">
+        <v>0.0384</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>8.842529421797714</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.09764952733214348</v>
+      </c>
+      <c r="C29">
+        <v>51.79579028426683</v>
+      </c>
+      <c r="D29">
+        <v>60.60279028426683</v>
+      </c>
+      <c r="E29">
+        <v>-21.723</v>
+      </c>
+      <c r="F29">
+        <v>12.177</v>
+      </c>
+      <c r="G29">
+        <v>3.37</v>
+      </c>
+      <c r="H29">
+        <v>11.2</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>5.05</v>
+      </c>
+      <c r="K29">
+        <v>0.073</v>
+      </c>
+      <c r="L29">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M29">
+        <v>0.584496</v>
+      </c>
+      <c r="N29">
+        <v>4.392504</v>
+      </c>
+      <c r="O29">
+        <v>0.8785008</v>
+      </c>
+      <c r="P29">
+        <v>3.5140032</v>
+      </c>
+      <c r="Q29">
+        <v>3.5870032</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1195637360714294</v>
+      </c>
+      <c r="T29">
+        <v>0.7221704572877506</v>
+      </c>
+      <c r="U29">
+        <v>0.048</v>
+      </c>
+      <c r="V29">
+        <v>0.2</v>
+      </c>
+      <c r="W29">
+        <v>0.0384</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>8.515028332101501</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.09752088139698037</v>
+      </c>
+      <c r="C30">
+        <v>51.4775591127336</v>
+      </c>
+      <c r="D30">
+        <v>60.7355591127336</v>
+      </c>
+      <c r="E30">
+        <v>-21.272</v>
+      </c>
+      <c r="F30">
+        <v>12.628</v>
+      </c>
+      <c r="G30">
+        <v>3.37</v>
+      </c>
+      <c r="H30">
+        <v>11.2</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>5.05</v>
+      </c>
+      <c r="K30">
+        <v>0.073</v>
+      </c>
+      <c r="L30">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M30">
+        <v>0.606144</v>
+      </c>
+      <c r="N30">
+        <v>4.370856</v>
+      </c>
+      <c r="O30">
+        <v>0.8741712</v>
+      </c>
+      <c r="P30">
+        <v>3.4966848</v>
+      </c>
+      <c r="Q30">
+        <v>3.5696848</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1205123352735838</v>
+      </c>
+      <c r="T30">
+        <v>0.7306526097106746</v>
+      </c>
+      <c r="U30">
+        <v>0.048</v>
+      </c>
+      <c r="V30">
+        <v>0.2</v>
+      </c>
+      <c r="W30">
+        <v>0.0384</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>8.210920177383592</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.09739223546181727</v>
+      </c>
+      <c r="C31">
+        <v>51.15991095940966</v>
+      </c>
+      <c r="D31">
+        <v>60.86891095940965</v>
+      </c>
+      <c r="E31">
+        <v>-20.821</v>
+      </c>
+      <c r="F31">
+        <v>13.079</v>
+      </c>
+      <c r="G31">
+        <v>3.37</v>
+      </c>
+      <c r="H31">
+        <v>11.2</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>5.05</v>
+      </c>
+      <c r="K31">
+        <v>0.073</v>
+      </c>
+      <c r="L31">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M31">
+        <v>0.6277919999999999</v>
+      </c>
+      <c r="N31">
+        <v>4.349207999999999</v>
+      </c>
+      <c r="O31">
+        <v>0.8698415999999999</v>
+      </c>
+      <c r="P31">
+        <v>3.479366399999999</v>
+      </c>
+      <c r="Q31">
+        <v>3.552366399999999</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1214876555800243</v>
+      </c>
+      <c r="T31">
+        <v>0.739373696004667</v>
+      </c>
+      <c r="U31">
+        <v>0.048</v>
+      </c>
+      <c r="V31">
+        <v>0.2</v>
+      </c>
+      <c r="W31">
+        <v>0.0384</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>7.927784998853123</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.09762358952665419</v>
+      </c>
+      <c r="C32">
+        <v>50.46951261452838</v>
+      </c>
+      <c r="D32">
+        <v>60.62951261452839</v>
+      </c>
+      <c r="E32">
+        <v>-20.37</v>
+      </c>
+      <c r="F32">
+        <v>13.53</v>
+      </c>
+      <c r="G32">
+        <v>3.37</v>
+      </c>
+      <c r="H32">
+        <v>11.2</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>5.05</v>
+      </c>
+      <c r="K32">
+        <v>0.073</v>
+      </c>
+      <c r="L32">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M32">
+        <v>0.6697349999999999</v>
+      </c>
+      <c r="N32">
+        <v>4.307264999999999</v>
+      </c>
+      <c r="O32">
+        <v>0.8614529999999999</v>
+      </c>
+      <c r="P32">
+        <v>3.445811999999999</v>
+      </c>
+      <c r="Q32">
+        <v>3.518811999999999</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1224908421809346</v>
+      </c>
+      <c r="T32">
+        <v>0.7483439561927734</v>
+      </c>
+      <c r="U32">
+        <v>0.0495</v>
+      </c>
+      <c r="V32">
+        <v>0.2</v>
+      </c>
+      <c r="W32">
+        <v>0.0396</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>7.431297453470402</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.09750694359149109</v>
+      </c>
+      <c r="C33">
+        <v>50.13897853839961</v>
+      </c>
+      <c r="D33">
+        <v>60.74997853839961</v>
+      </c>
+      <c r="E33">
+        <v>-19.919</v>
+      </c>
+      <c r="F33">
+        <v>13.981</v>
+      </c>
+      <c r="G33">
+        <v>3.37</v>
+      </c>
+      <c r="H33">
+        <v>11.2</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>5.05</v>
+      </c>
+      <c r="K33">
+        <v>0.073</v>
+      </c>
+      <c r="L33">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M33">
+        <v>0.6920594999999999</v>
+      </c>
+      <c r="N33">
+        <v>4.284940499999999</v>
+      </c>
+      <c r="O33">
+        <v>0.8569880999999999</v>
+      </c>
+      <c r="P33">
+        <v>3.4279524</v>
+      </c>
+      <c r="Q33">
+        <v>3.5009524</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1235231066543349</v>
+      </c>
+      <c r="T33">
+        <v>0.7575742239225639</v>
+      </c>
+      <c r="U33">
+        <v>0.0495</v>
+      </c>
+      <c r="V33">
+        <v>0.2</v>
+      </c>
+      <c r="W33">
+        <v>0.0396</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>7.191578180777809</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.09739029765632799</v>
+      </c>
+      <c r="C34">
+        <v>49.80892412736581</v>
+      </c>
+      <c r="D34">
+        <v>60.87092412736582</v>
+      </c>
+      <c r="E34">
+        <v>-19.468</v>
+      </c>
+      <c r="F34">
+        <v>14.432</v>
+      </c>
+      <c r="G34">
+        <v>3.37</v>
+      </c>
+      <c r="H34">
+        <v>11.2</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>5.05</v>
+      </c>
+      <c r="K34">
+        <v>0.073</v>
+      </c>
+      <c r="L34">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M34">
+        <v>0.714384</v>
+      </c>
+      <c r="N34">
+        <v>4.262616</v>
+      </c>
+      <c r="O34">
+        <v>0.8525231999999999</v>
+      </c>
+      <c r="P34">
+        <v>3.4100928</v>
+      </c>
+      <c r="Q34">
+        <v>3.4830928</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1245857318475412</v>
+      </c>
+      <c r="T34">
+        <v>0.7670759701149954</v>
+      </c>
+      <c r="U34">
+        <v>0.0495</v>
+      </c>
+      <c r="V34">
+        <v>0.2</v>
+      </c>
+      <c r="W34">
+        <v>0.0396</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>6.966841362628501</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.09727365172116489</v>
+      </c>
+      <c r="C35">
+        <v>49.47935225200111</v>
+      </c>
+      <c r="D35">
+        <v>60.9923522520011</v>
+      </c>
+      <c r="E35">
+        <v>-19.017</v>
+      </c>
+      <c r="F35">
+        <v>14.883</v>
+      </c>
+      <c r="G35">
+        <v>3.37</v>
+      </c>
+      <c r="H35">
+        <v>11.2</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>5.05</v>
+      </c>
+      <c r="K35">
+        <v>0.073</v>
+      </c>
+      <c r="L35">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M35">
+        <v>0.7367085</v>
+      </c>
+      <c r="N35">
+        <v>4.2402915</v>
+      </c>
+      <c r="O35">
+        <v>0.8480582999999999</v>
+      </c>
+      <c r="P35">
+        <v>3.3922332</v>
+      </c>
+      <c r="Q35">
+        <v>3.4652332</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1256800771957685</v>
+      </c>
+      <c r="T35">
+        <v>0.7768613505221263</v>
+      </c>
+      <c r="U35">
+        <v>0.0495</v>
+      </c>
+      <c r="V35">
+        <v>0.2</v>
+      </c>
+      <c r="W35">
+        <v>0.0396</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>6.755724957700365</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.09715700578600181</v>
+      </c>
+      <c r="C36">
+        <v>49.1502658058308</v>
+      </c>
+      <c r="D36">
+        <v>61.1142658058308</v>
+      </c>
+      <c r="E36">
+        <v>-18.566</v>
+      </c>
+      <c r="F36">
+        <v>15.334</v>
+      </c>
+      <c r="G36">
+        <v>3.37</v>
+      </c>
+      <c r="H36">
+        <v>11.2</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>5.05</v>
+      </c>
+      <c r="K36">
+        <v>0.073</v>
+      </c>
+      <c r="L36">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M36">
+        <v>0.7590330000000001</v>
+      </c>
+      <c r="N36">
+        <v>4.217967</v>
+      </c>
+      <c r="O36">
+        <v>0.8435934</v>
+      </c>
+      <c r="P36">
+        <v>3.3743736</v>
+      </c>
+      <c r="Q36">
+        <v>3.4473736</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1268075845242452</v>
+      </c>
+      <c r="T36">
+        <v>0.7869432576082612</v>
+      </c>
+      <c r="U36">
+        <v>0.0495</v>
+      </c>
+      <c r="V36">
+        <v>0.2</v>
+      </c>
+      <c r="W36">
+        <v>0.0396</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>6.557027164826825</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.09704035985083871</v>
+      </c>
+      <c r="C37">
+        <v>48.82166770556124</v>
+      </c>
+      <c r="D37">
+        <v>61.23666770556124</v>
+      </c>
+      <c r="E37">
+        <v>-18.115</v>
+      </c>
+      <c r="F37">
+        <v>15.785</v>
+      </c>
+      <c r="G37">
+        <v>3.37</v>
+      </c>
+      <c r="H37">
+        <v>11.2</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>5.05</v>
+      </c>
+      <c r="K37">
+        <v>0.073</v>
+      </c>
+      <c r="L37">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M37">
+        <v>0.7813575</v>
+      </c>
+      <c r="N37">
+        <v>4.195642499999999</v>
+      </c>
+      <c r="O37">
+        <v>0.8391284999999998</v>
+      </c>
+      <c r="P37">
+        <v>3.356513999999999</v>
+      </c>
+      <c r="Q37">
+        <v>3.429513999999999</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1279697843859057</v>
+      </c>
+      <c r="T37">
+        <v>0.7973353772201235</v>
+      </c>
+      <c r="U37">
+        <v>0.0495</v>
+      </c>
+      <c r="V37">
+        <v>0.2</v>
+      </c>
+      <c r="W37">
+        <v>0.0396</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>6.369683531546058</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.09692371391567563</v>
+      </c>
+      <c r="C38">
+        <v>48.49356089131239</v>
+      </c>
+      <c r="D38">
+        <v>61.35956089131239</v>
+      </c>
+      <c r="E38">
+        <v>-17.664</v>
+      </c>
+      <c r="F38">
+        <v>16.236</v>
+      </c>
+      <c r="G38">
+        <v>3.37</v>
+      </c>
+      <c r="H38">
+        <v>11.2</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>5.05</v>
+      </c>
+      <c r="K38">
+        <v>0.073</v>
+      </c>
+      <c r="L38">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M38">
+        <v>0.8036819999999999</v>
+      </c>
+      <c r="N38">
+        <v>4.173317999999999</v>
+      </c>
+      <c r="O38">
+        <v>0.8346635999999998</v>
+      </c>
+      <c r="P38">
+        <v>3.338654399999999</v>
+      </c>
+      <c r="Q38">
+        <v>3.411654399999999</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1291683029932432</v>
+      </c>
+      <c r="T38">
+        <v>0.8080522505698562</v>
+      </c>
+      <c r="U38">
+        <v>0.0495</v>
+      </c>
+      <c r="V38">
+        <v>0.2</v>
+      </c>
+      <c r="W38">
+        <v>0.0396</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>6.192747877892002</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.09722146798051254</v>
+      </c>
+      <c r="C39">
+        <v>47.72983238065446</v>
+      </c>
+      <c r="D39">
+        <v>61.04683238065445</v>
+      </c>
+      <c r="E39">
+        <v>-17.213</v>
+      </c>
+      <c r="F39">
+        <v>16.687</v>
+      </c>
+      <c r="G39">
+        <v>3.37</v>
+      </c>
+      <c r="H39">
+        <v>11.2</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>5.05</v>
+      </c>
+      <c r="K39">
+        <v>0.073</v>
+      </c>
+      <c r="L39">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M39">
+        <v>0.8493682999999999</v>
+      </c>
+      <c r="N39">
+        <v>4.127631699999999</v>
+      </c>
+      <c r="O39">
+        <v>0.8255263399999999</v>
+      </c>
+      <c r="P39">
+        <v>3.30210536</v>
+      </c>
+      <c r="Q39">
+        <v>3.37510536</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1304048698103374</v>
+      </c>
+      <c r="T39">
+        <v>0.819109342121168</v>
+      </c>
+      <c r="U39">
+        <v>0.0509</v>
+      </c>
+      <c r="V39">
+        <v>0.2</v>
+      </c>
+      <c r="W39">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>5.859648870813756</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.09711602204534943</v>
+      </c>
+      <c r="C40">
+        <v>47.38921611574732</v>
+      </c>
+      <c r="D40">
+        <v>61.15721611574732</v>
+      </c>
+      <c r="E40">
+        <v>-16.762</v>
+      </c>
+      <c r="F40">
+        <v>17.138</v>
+      </c>
+      <c r="G40">
+        <v>3.37</v>
+      </c>
+      <c r="H40">
+        <v>11.2</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>5.05</v>
+      </c>
+      <c r="K40">
+        <v>0.073</v>
+      </c>
+      <c r="L40">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M40">
+        <v>0.8723241999999999</v>
+      </c>
+      <c r="N40">
+        <v>4.1046758</v>
+      </c>
+      <c r="O40">
+        <v>0.82093516</v>
+      </c>
+      <c r="P40">
+        <v>3.28374064</v>
+      </c>
+      <c r="Q40">
+        <v>3.35674064</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1316813258795959</v>
+      </c>
+      <c r="T40">
+        <v>0.8305231140451025</v>
+      </c>
+      <c r="U40">
+        <v>0.0509</v>
+      </c>
+      <c r="V40">
+        <v>0.2</v>
+      </c>
+      <c r="W40">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>5.70544758473971</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.09701057611018635</v>
+      </c>
+      <c r="C41">
+        <v>47.04899976154202</v>
+      </c>
+      <c r="D41">
+        <v>61.26799976154201</v>
+      </c>
+      <c r="E41">
+        <v>-16.311</v>
+      </c>
+      <c r="F41">
+        <v>17.589</v>
+      </c>
+      <c r="G41">
+        <v>3.37</v>
+      </c>
+      <c r="H41">
+        <v>11.2</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>5.05</v>
+      </c>
+      <c r="K41">
+        <v>0.073</v>
+      </c>
+      <c r="L41">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M41">
+        <v>0.8952800999999999</v>
+      </c>
+      <c r="N41">
+        <v>4.0817199</v>
+      </c>
+      <c r="O41">
+        <v>0.81634398</v>
+      </c>
+      <c r="P41">
+        <v>3.265375919999999</v>
+      </c>
+      <c r="Q41">
+        <v>3.338375919999999</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1329996329675186</v>
+      </c>
+      <c r="T41">
+        <v>0.8423111079993302</v>
+      </c>
+      <c r="U41">
+        <v>0.0509</v>
+      </c>
+      <c r="V41">
+        <v>0.2</v>
+      </c>
+      <c r="W41">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>5.559154056925872</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.09690513017502325</v>
+      </c>
+      <c r="C42">
+        <v>46.70918549524517</v>
+      </c>
+      <c r="D42">
+        <v>61.37918549524517</v>
+      </c>
+      <c r="E42">
+        <v>-15.86</v>
+      </c>
+      <c r="F42">
+        <v>18.04</v>
+      </c>
+      <c r="G42">
+        <v>3.37</v>
+      </c>
+      <c r="H42">
+        <v>11.2</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>5.05</v>
+      </c>
+      <c r="K42">
+        <v>0.073</v>
+      </c>
+      <c r="L42">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M42">
+        <v>0.9182359999999999</v>
+      </c>
+      <c r="N42">
+        <v>4.058763999999999</v>
+      </c>
+      <c r="O42">
+        <v>0.8117527999999998</v>
+      </c>
+      <c r="P42">
+        <v>3.247011199999999</v>
+      </c>
+      <c r="Q42">
+        <v>3.320011199999999</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1343618836250388</v>
+      </c>
+      <c r="T42">
+        <v>0.8544920350853653</v>
+      </c>
+      <c r="U42">
+        <v>0.0509</v>
+      </c>
+      <c r="V42">
+        <v>0.2</v>
+      </c>
+      <c r="W42">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>5.420175205502725</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.09679968423986017</v>
+      </c>
+      <c r="C43">
+        <v>46.36977550989644</v>
+      </c>
+      <c r="D43">
+        <v>61.49077550989644</v>
+      </c>
+      <c r="E43">
+        <v>-15.409</v>
+      </c>
+      <c r="F43">
+        <v>18.491</v>
+      </c>
+      <c r="G43">
+        <v>3.37</v>
+      </c>
+      <c r="H43">
+        <v>11.2</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>5.05</v>
+      </c>
+      <c r="K43">
+        <v>0.073</v>
+      </c>
+      <c r="L43">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M43">
+        <v>0.9411919</v>
+      </c>
+      <c r="N43">
+        <v>4.0358081</v>
+      </c>
+      <c r="O43">
+        <v>0.80716162</v>
+      </c>
+      <c r="P43">
+        <v>3.22864648</v>
+      </c>
+      <c r="Q43">
+        <v>3.30164648</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1357703122709494</v>
+      </c>
+      <c r="T43">
+        <v>0.8670858749539779</v>
+      </c>
+      <c r="U43">
+        <v>0.0509</v>
+      </c>
+      <c r="V43">
+        <v>0.2</v>
+      </c>
+      <c r="W43">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>5.287975810246561</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.09669423830469707</v>
+      </c>
+      <c r="C44">
+        <v>46.03077201451268</v>
+      </c>
+      <c r="D44">
+        <v>61.60277201451267</v>
+      </c>
+      <c r="E44">
+        <v>-14.958</v>
+      </c>
+      <c r="F44">
+        <v>18.942</v>
+      </c>
+      <c r="G44">
+        <v>3.37</v>
+      </c>
+      <c r="H44">
+        <v>11.2</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>5.05</v>
+      </c>
+      <c r="K44">
+        <v>0.073</v>
+      </c>
+      <c r="L44">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M44">
+        <v>0.9641477999999999</v>
+      </c>
+      <c r="N44">
+        <v>4.012852199999999</v>
+      </c>
+      <c r="O44">
+        <v>0.8025704399999999</v>
+      </c>
+      <c r="P44">
+        <v>3.21028176</v>
+      </c>
+      <c r="Q44">
+        <v>3.283281759999999</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1372273074218915</v>
+      </c>
+      <c r="T44">
+        <v>0.8801139851628873</v>
+      </c>
+      <c r="U44">
+        <v>0.0509</v>
+      </c>
+      <c r="V44">
+        <v>0.2</v>
+      </c>
+      <c r="W44">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>5.162071624288309</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.09658879236953398</v>
+      </c>
+      <c r="C45">
+        <v>45.69217723423367</v>
+      </c>
+      <c r="D45">
+        <v>61.71517723423367</v>
+      </c>
+      <c r="E45">
+        <v>-14.507</v>
+      </c>
+      <c r="F45">
+        <v>19.393</v>
+      </c>
+      <c r="G45">
+        <v>3.37</v>
+      </c>
+      <c r="H45">
+        <v>11.2</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>5.05</v>
+      </c>
+      <c r="K45">
+        <v>0.073</v>
+      </c>
+      <c r="L45">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M45">
+        <v>0.9871036999999999</v>
+      </c>
+      <c r="N45">
+        <v>3.989896299999999</v>
+      </c>
+      <c r="O45">
+        <v>0.79797926</v>
+      </c>
+      <c r="P45">
+        <v>3.191917039999999</v>
+      </c>
+      <c r="Q45">
+        <v>3.264917039999999</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1387354252097087</v>
+      </c>
+      <c r="T45">
+        <v>0.8935992220457939</v>
+      </c>
+      <c r="U45">
+        <v>0.0509</v>
+      </c>
+      <c r="V45">
+        <v>0.2</v>
+      </c>
+      <c r="W45">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>5.042023446979279</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.09648334643437087</v>
+      </c>
+      <c r="C46">
+        <v>45.35399341046966</v>
+      </c>
+      <c r="D46">
+        <v>61.82799341046965</v>
+      </c>
+      <c r="E46">
+        <v>-14.056</v>
+      </c>
+      <c r="F46">
+        <v>19.844</v>
+      </c>
+      <c r="G46">
+        <v>3.37</v>
+      </c>
+      <c r="H46">
+        <v>11.2</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>5.05</v>
+      </c>
+      <c r="K46">
+        <v>0.073</v>
+      </c>
+      <c r="L46">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M46">
+        <v>1.0100596</v>
+      </c>
+      <c r="N46">
+        <v>3.966940399999999</v>
+      </c>
+      <c r="O46">
+        <v>0.7933880799999999</v>
+      </c>
+      <c r="P46">
+        <v>3.17355232</v>
+      </c>
+      <c r="Q46">
+        <v>3.24655232</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1402974043470908</v>
+      </c>
+      <c r="T46">
+        <v>0.9075660745316612</v>
+      </c>
+      <c r="U46">
+        <v>0.0509</v>
+      </c>
+      <c r="V46">
+        <v>0.2</v>
+      </c>
+      <c r="W46">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>4.927432005002476</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.09637790049920779</v>
+      </c>
+      <c r="C47">
+        <v>45.01622280105003</v>
+      </c>
+      <c r="D47">
+        <v>61.94122280105004</v>
+      </c>
+      <c r="E47">
+        <v>-13.605</v>
+      </c>
+      <c r="F47">
+        <v>20.295</v>
+      </c>
+      <c r="G47">
+        <v>3.37</v>
+      </c>
+      <c r="H47">
+        <v>11.2</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>5.05</v>
+      </c>
+      <c r="K47">
+        <v>0.073</v>
+      </c>
+      <c r="L47">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M47">
+        <v>1.0330155</v>
+      </c>
+      <c r="N47">
+        <v>3.9439845</v>
+      </c>
+      <c r="O47">
+        <v>0.7887968999999999</v>
+      </c>
+      <c r="P47">
+        <v>3.1551876</v>
+      </c>
+      <c r="Q47">
+        <v>3.2281876</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1419161827258323</v>
+      </c>
+      <c r="T47">
+        <v>0.9220408125624692</v>
+      </c>
+      <c r="U47">
+        <v>0.0509</v>
+      </c>
+      <c r="V47">
+        <v>0.2</v>
+      </c>
+      <c r="W47">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>4.817933516002422</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.09627245456404471</v>
+      </c>
+      <c r="C48">
+        <v>44.67886768037434</v>
+      </c>
+      <c r="D48">
+        <v>62.05486768037434</v>
+      </c>
+      <c r="E48">
+        <v>-13.154</v>
+      </c>
+      <c r="F48">
+        <v>20.746</v>
+      </c>
+      <c r="G48">
+        <v>3.37</v>
+      </c>
+      <c r="H48">
+        <v>11.2</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>5.05</v>
+      </c>
+      <c r="K48">
+        <v>0.073</v>
+      </c>
+      <c r="L48">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M48">
+        <v>1.0559714</v>
+      </c>
+      <c r="N48">
+        <v>3.9210286</v>
+      </c>
+      <c r="O48">
+        <v>0.78420572</v>
+      </c>
+      <c r="P48">
+        <v>3.13682288</v>
+      </c>
+      <c r="Q48">
+        <v>3.209822879999999</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.143594915859342</v>
+      </c>
+      <c r="T48">
+        <v>0.9370516520018257</v>
+      </c>
+      <c r="U48">
+        <v>0.0509</v>
+      </c>
+      <c r="V48">
+        <v>0.2</v>
+      </c>
+      <c r="W48">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>4.713195830871934</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.0961670086288816</v>
+      </c>
+      <c r="C49">
+        <v>44.34193033956423</v>
+      </c>
+      <c r="D49">
+        <v>62.16893033956423</v>
+      </c>
+      <c r="E49">
+        <v>-12.703</v>
+      </c>
+      <c r="F49">
+        <v>21.197</v>
+      </c>
+      <c r="G49">
+        <v>3.37</v>
+      </c>
+      <c r="H49">
+        <v>11.2</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>5.05</v>
+      </c>
+      <c r="K49">
+        <v>0.073</v>
+      </c>
+      <c r="L49">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M49">
+        <v>1.0789273</v>
+      </c>
+      <c r="N49">
+        <v>3.898072699999999</v>
+      </c>
+      <c r="O49">
+        <v>0.7796145399999999</v>
+      </c>
+      <c r="P49">
+        <v>3.118458159999999</v>
+      </c>
+      <c r="Q49">
+        <v>3.191458159999999</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1453369974129841</v>
+      </c>
+      <c r="T49">
+        <v>0.9526289382124786</v>
+      </c>
+      <c r="U49">
+        <v>0.0509</v>
+      </c>
+      <c r="V49">
+        <v>0.2</v>
+      </c>
+      <c r="W49">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>4.612915068512956</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.09606156269371852</v>
+      </c>
+      <c r="C50">
+        <v>44.00541308661758</v>
+      </c>
+      <c r="D50">
+        <v>62.28341308661757</v>
+      </c>
+      <c r="E50">
+        <v>-12.252</v>
+      </c>
+      <c r="F50">
+        <v>21.648</v>
+      </c>
+      <c r="G50">
+        <v>3.37</v>
+      </c>
+      <c r="H50">
+        <v>11.2</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>5.05</v>
+      </c>
+      <c r="K50">
+        <v>0.073</v>
+      </c>
+      <c r="L50">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M50">
+        <v>1.1018832</v>
+      </c>
+      <c r="N50">
+        <v>3.8751168</v>
+      </c>
+      <c r="O50">
+        <v>0.7750233600000001</v>
+      </c>
+      <c r="P50">
+        <v>3.10009344</v>
+      </c>
+      <c r="Q50">
+        <v>3.17309344</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1471460821033048</v>
+      </c>
+      <c r="T50">
+        <v>0.968805350815849</v>
+      </c>
+      <c r="U50">
+        <v>0.0509</v>
+      </c>
+      <c r="V50">
+        <v>0.2</v>
+      </c>
+      <c r="W50">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>4.516812671252271</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.0969753167585554</v>
+      </c>
+      <c r="C51">
+        <v>42.5761335507104</v>
+      </c>
+      <c r="D51">
+        <v>61.3051335507104</v>
+      </c>
+      <c r="E51">
+        <v>-11.801</v>
+      </c>
+      <c r="F51">
+        <v>22.099</v>
+      </c>
+      <c r="G51">
+        <v>3.37</v>
+      </c>
+      <c r="H51">
+        <v>11.2</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>5.05</v>
+      </c>
+      <c r="K51">
+        <v>0.073</v>
+      </c>
+      <c r="L51">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M51">
+        <v>1.1822965</v>
+      </c>
+      <c r="N51">
+        <v>3.7947035</v>
+      </c>
+      <c r="O51">
+        <v>0.7589407</v>
+      </c>
+      <c r="P51">
+        <v>3.0357628</v>
+      </c>
+      <c r="Q51">
+        <v>3.1087628</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1490261112912851</v>
+      </c>
+      <c r="T51">
+        <v>0.98561613254092</v>
+      </c>
+      <c r="U51">
+        <v>0.0535</v>
+      </c>
+      <c r="V51">
+        <v>0.2</v>
+      </c>
+      <c r="W51">
+        <v>0.0428</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>4.209603936068491</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.09689067082339231</v>
+      </c>
+      <c r="C52">
+        <v>42.21446339121913</v>
+      </c>
+      <c r="D52">
+        <v>61.39446339121912</v>
+      </c>
+      <c r="E52">
+        <v>-11.35</v>
+      </c>
+      <c r="F52">
+        <v>22.55</v>
+      </c>
+      <c r="G52">
+        <v>3.37</v>
+      </c>
+      <c r="H52">
+        <v>11.2</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>5.05</v>
+      </c>
+      <c r="K52">
+        <v>0.073</v>
+      </c>
+      <c r="L52">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M52">
+        <v>1.206425</v>
+      </c>
+      <c r="N52">
+        <v>3.770575</v>
+      </c>
+      <c r="O52">
+        <v>0.754115</v>
+      </c>
+      <c r="P52">
+        <v>3.016459999999999</v>
+      </c>
+      <c r="Q52">
+        <v>3.089459999999999</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1509813416467846</v>
+      </c>
+      <c r="T52">
+        <v>1.003099345534994</v>
+      </c>
+      <c r="U52">
+        <v>0.0535</v>
+      </c>
+      <c r="V52">
+        <v>0.2</v>
+      </c>
+      <c r="W52">
+        <v>0.0428</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>4.125411857347121</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.09680602488822923</v>
+      </c>
+      <c r="C53">
+        <v>41.85305394284887</v>
+      </c>
+      <c r="D53">
+        <v>61.48405394284887</v>
+      </c>
+      <c r="E53">
+        <v>-10.899</v>
+      </c>
+      <c r="F53">
+        <v>23.001</v>
+      </c>
+      <c r="G53">
+        <v>3.37</v>
+      </c>
+      <c r="H53">
+        <v>11.2</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>5.05</v>
+      </c>
+      <c r="K53">
+        <v>0.073</v>
+      </c>
+      <c r="L53">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M53">
+        <v>1.2305535</v>
+      </c>
+      <c r="N53">
+        <v>3.746446499999999</v>
+      </c>
+      <c r="O53">
+        <v>0.7492892999999999</v>
+      </c>
+      <c r="P53">
+        <v>2.997157199999999</v>
+      </c>
+      <c r="Q53">
+        <v>3.070157199999999</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1530163773229168</v>
+      </c>
+      <c r="T53">
+        <v>1.021296159059438</v>
+      </c>
+      <c r="U53">
+        <v>0.0535</v>
+      </c>
+      <c r="V53">
+        <v>0.2</v>
+      </c>
+      <c r="W53">
+        <v>0.0428</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>4.044521428771686</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.09784457895306611</v>
+      </c>
+      <c r="C54">
+        <v>40.32059116883615</v>
+      </c>
+      <c r="D54">
+        <v>60.40259116883615</v>
+      </c>
+      <c r="E54">
+        <v>-10.448</v>
+      </c>
+      <c r="F54">
+        <v>23.452</v>
+      </c>
+      <c r="G54">
+        <v>3.37</v>
+      </c>
+      <c r="H54">
+        <v>11.2</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>5.05</v>
+      </c>
+      <c r="K54">
+        <v>0.073</v>
+      </c>
+      <c r="L54">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M54">
+        <v>1.3180024</v>
+      </c>
+      <c r="N54">
+        <v>3.658997599999999</v>
+      </c>
+      <c r="O54">
+        <v>0.7317995199999999</v>
+      </c>
+      <c r="P54">
+        <v>2.927198079999999</v>
+      </c>
+      <c r="Q54">
+        <v>3.000198079999999</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1551362061522211</v>
+      </c>
+      <c r="T54">
+        <v>1.040251173147401</v>
+      </c>
+      <c r="U54">
+        <v>0.0562</v>
+      </c>
+      <c r="V54">
+        <v>0.2</v>
+      </c>
+      <c r="W54">
+        <v>0.04496</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>3.776169148098668</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.09778153301790303</v>
+      </c>
+      <c r="C55">
+        <v>39.93415608689885</v>
+      </c>
+      <c r="D55">
+        <v>60.46715608689885</v>
+      </c>
+      <c r="E55">
+        <v>-9.997</v>
+      </c>
+      <c r="F55">
+        <v>23.903</v>
+      </c>
+      <c r="G55">
+        <v>3.37</v>
+      </c>
+      <c r="H55">
+        <v>11.2</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>5.05</v>
+      </c>
+      <c r="K55">
+        <v>0.073</v>
+      </c>
+      <c r="L55">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M55">
+        <v>1.3433486</v>
+      </c>
+      <c r="N55">
+        <v>3.6336514</v>
+      </c>
+      <c r="O55">
+        <v>0.72673028</v>
+      </c>
+      <c r="P55">
+        <v>2.90692112</v>
+      </c>
+      <c r="Q55">
+        <v>2.97992112</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1573462404636235</v>
+      </c>
+      <c r="T55">
+        <v>1.060012783579533</v>
+      </c>
+      <c r="U55">
+        <v>0.0562</v>
+      </c>
+      <c r="V55">
+        <v>0.2</v>
+      </c>
+      <c r="W55">
+        <v>0.04496</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>3.704920673606241</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.09771848708273993</v>
+      </c>
+      <c r="C56">
+        <v>39.5478591807987</v>
+      </c>
+      <c r="D56">
+        <v>60.5318591807987</v>
+      </c>
+      <c r="E56">
+        <v>-9.545999999999999</v>
+      </c>
+      <c r="F56">
+        <v>24.354</v>
+      </c>
+      <c r="G56">
+        <v>3.37</v>
+      </c>
+      <c r="H56">
+        <v>11.2</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>5.05</v>
+      </c>
+      <c r="K56">
+        <v>0.073</v>
+      </c>
+      <c r="L56">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M56">
+        <v>1.3686948</v>
+      </c>
+      <c r="N56">
+        <v>3.608305199999999</v>
+      </c>
+      <c r="O56">
+        <v>0.7216610399999999</v>
+      </c>
+      <c r="P56">
+        <v>2.886644159999999</v>
+      </c>
+      <c r="Q56">
+        <v>2.959644159999999</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1596523632233477</v>
+      </c>
+      <c r="T56">
+        <v>1.080633594465235</v>
+      </c>
+      <c r="U56">
+        <v>0.0562</v>
+      </c>
+      <c r="V56">
+        <v>0.2</v>
+      </c>
+      <c r="W56">
+        <v>0.04496</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>3.636311031502421</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.09765544114757682</v>
+      </c>
+      <c r="C57">
+        <v>39.16170089457747</v>
+      </c>
+      <c r="D57">
+        <v>60.59670089457747</v>
+      </c>
+      <c r="E57">
+        <v>-9.094999999999999</v>
+      </c>
+      <c r="F57">
+        <v>24.805</v>
+      </c>
+      <c r="G57">
+        <v>3.37</v>
+      </c>
+      <c r="H57">
+        <v>11.2</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>5.05</v>
+      </c>
+      <c r="K57">
+        <v>0.073</v>
+      </c>
+      <c r="L57">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M57">
+        <v>1.394041</v>
+      </c>
+      <c r="N57">
+        <v>3.582958999999999</v>
+      </c>
+      <c r="O57">
+        <v>0.7165917999999999</v>
+      </c>
+      <c r="P57">
+        <v>2.8663672</v>
+      </c>
+      <c r="Q57">
+        <v>2.9393672</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1620609803279485</v>
+      </c>
+      <c r="T57">
+        <v>1.102170885834747</v>
+      </c>
+      <c r="U57">
+        <v>0.0562</v>
+      </c>
+      <c r="V57">
+        <v>0.2</v>
+      </c>
+      <c r="W57">
+        <v>0.04496</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>3.570196285475104</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.09759239521241375</v>
+      </c>
+      <c r="C58">
+        <v>38.77568167418158</v>
+      </c>
+      <c r="D58">
+        <v>60.66168167418158</v>
+      </c>
+      <c r="E58">
+        <v>-8.643999999999998</v>
+      </c>
+      <c r="F58">
+        <v>25.256</v>
+      </c>
+      <c r="G58">
+        <v>3.37</v>
+      </c>
+      <c r="H58">
+        <v>11.2</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>5.05</v>
+      </c>
+      <c r="K58">
+        <v>0.073</v>
+      </c>
+      <c r="L58">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M58">
+        <v>1.4193872</v>
+      </c>
+      <c r="N58">
+        <v>3.557612799999999</v>
+      </c>
+      <c r="O58">
+        <v>0.7115225599999999</v>
+      </c>
+      <c r="P58">
+        <v>2.84609024</v>
+      </c>
+      <c r="Q58">
+        <v>2.91909024</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1645790800282131</v>
+      </c>
+      <c r="T58">
+        <v>1.124687144993781</v>
+      </c>
+      <c r="U58">
+        <v>0.0562</v>
+      </c>
+      <c r="V58">
+        <v>0.2</v>
+      </c>
+      <c r="W58">
+        <v>0.04496</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>3.506442780377334</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.09967254927725067</v>
+      </c>
+      <c r="C59">
+        <v>36.25173343704326</v>
+      </c>
+      <c r="D59">
+        <v>58.58873343704327</v>
+      </c>
+      <c r="E59">
+        <v>-8.192999999999998</v>
+      </c>
+      <c r="F59">
+        <v>25.707</v>
+      </c>
+      <c r="G59">
+        <v>3.37</v>
+      </c>
+      <c r="H59">
+        <v>11.2</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>5.05</v>
+      </c>
+      <c r="K59">
+        <v>0.073</v>
+      </c>
+      <c r="L59">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M59">
+        <v>1.5655563</v>
+      </c>
+      <c r="N59">
+        <v>3.4114437</v>
+      </c>
+      <c r="O59">
+        <v>0.6822887399999999</v>
+      </c>
+      <c r="P59">
+        <v>2.72915496</v>
+      </c>
+      <c r="Q59">
+        <v>2.80215496</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.167214300644769</v>
+      </c>
+      <c r="T59">
+        <v>1.148250672020678</v>
+      </c>
+      <c r="U59">
+        <v>0.0609</v>
+      </c>
+      <c r="V59">
+        <v>0.2</v>
+      </c>
+      <c r="W59">
+        <v>0.04872000000000001</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>3.179061653675437</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.09964710334208754</v>
+      </c>
+      <c r="C60">
+        <v>35.82523493391728</v>
+      </c>
+      <c r="D60">
+        <v>58.61323493391728</v>
+      </c>
+      <c r="E60">
+        <v>-7.742000000000004</v>
+      </c>
+      <c r="F60">
+        <v>26.15799999999999</v>
+      </c>
+      <c r="G60">
+        <v>3.37</v>
+      </c>
+      <c r="H60">
+        <v>11.2</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>5.05</v>
+      </c>
+      <c r="K60">
+        <v>0.073</v>
+      </c>
+      <c r="L60">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M60">
+        <v>1.5930222</v>
+      </c>
+      <c r="N60">
+        <v>3.3839778</v>
+      </c>
+      <c r="O60">
+        <v>0.67679556</v>
+      </c>
+      <c r="P60">
+        <v>2.70718224</v>
+      </c>
+      <c r="Q60">
+        <v>2.78018224</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1699750079573513</v>
+      </c>
+      <c r="T60">
+        <v>1.172936271763141</v>
+      </c>
+      <c r="U60">
+        <v>0.0609</v>
+      </c>
+      <c r="V60">
+        <v>0.2</v>
+      </c>
+      <c r="W60">
+        <v>0.04872000000000001</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>3.124250245853448</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.09962165740692447</v>
+      </c>
+      <c r="C61">
+        <v>35.3987569321563</v>
+      </c>
+      <c r="D61">
+        <v>58.63775693215629</v>
+      </c>
+      <c r="E61">
+        <v>-7.291000000000004</v>
+      </c>
+      <c r="F61">
+        <v>26.60899999999999</v>
+      </c>
+      <c r="G61">
+        <v>3.37</v>
+      </c>
+      <c r="H61">
+        <v>11.2</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>5.05</v>
+      </c>
+      <c r="K61">
+        <v>0.073</v>
+      </c>
+      <c r="L61">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M61">
+        <v>1.6204881</v>
+      </c>
+      <c r="N61">
+        <v>3.3565119</v>
+      </c>
+      <c r="O61">
+        <v>0.67130238</v>
+      </c>
+      <c r="P61">
+        <v>2.68520952</v>
+      </c>
+      <c r="Q61">
+        <v>2.75820952</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.172870383919328</v>
+      </c>
+      <c r="T61">
+        <v>1.198826047102798</v>
+      </c>
+      <c r="U61">
+        <v>0.0609</v>
+      </c>
+      <c r="V61">
+        <v>0.2</v>
+      </c>
+      <c r="W61">
+        <v>0.04872000000000001</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>3.071296851855932</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.09959621147176137</v>
+      </c>
+      <c r="C62">
+        <v>34.9722994575026</v>
+      </c>
+      <c r="D62">
+        <v>58.6622994575026</v>
+      </c>
+      <c r="E62">
+        <v>-6.840000000000003</v>
+      </c>
+      <c r="F62">
+        <v>27.06</v>
+      </c>
+      <c r="G62">
+        <v>3.37</v>
+      </c>
+      <c r="H62">
+        <v>11.2</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>5.05</v>
+      </c>
+      <c r="K62">
+        <v>0.073</v>
+      </c>
+      <c r="L62">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M62">
+        <v>1.647954</v>
+      </c>
+      <c r="N62">
+        <v>3.329046</v>
+      </c>
+      <c r="O62">
+        <v>0.6658092</v>
+      </c>
+      <c r="P62">
+        <v>2.6632368</v>
+      </c>
+      <c r="Q62">
+        <v>2.7362368</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1759105286794034</v>
+      </c>
+      <c r="T62">
+        <v>1.226010311209437</v>
+      </c>
+      <c r="U62">
+        <v>0.0609</v>
+      </c>
+      <c r="V62">
+        <v>0.2</v>
+      </c>
+      <c r="W62">
+        <v>0.04872000000000001</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>3.020108570991666</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1041091655365983</v>
+      </c>
+      <c r="C63">
+        <v>30.46765307243188</v>
+      </c>
+      <c r="D63">
+        <v>54.60865307243188</v>
+      </c>
+      <c r="E63">
+        <v>-6.389000000000003</v>
+      </c>
+      <c r="F63">
+        <v>27.511</v>
+      </c>
+      <c r="G63">
+        <v>3.37</v>
+      </c>
+      <c r="H63">
+        <v>11.2</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>5.05</v>
+      </c>
+      <c r="K63">
+        <v>0.073</v>
+      </c>
+      <c r="L63">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M63">
+        <v>1.9312722</v>
+      </c>
+      <c r="N63">
+        <v>3.0457278</v>
+      </c>
+      <c r="O63">
+        <v>0.60914556</v>
+      </c>
+      <c r="P63">
+        <v>2.43658224</v>
+      </c>
+      <c r="Q63">
+        <v>2.50958224</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1791065782989699</v>
+      </c>
+      <c r="T63">
+        <v>1.254588640142058</v>
+      </c>
+      <c r="U63">
+        <v>0.0702</v>
+      </c>
+      <c r="V63">
+        <v>0.2</v>
+      </c>
+      <c r="W63">
+        <v>0.05616</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>2.577057754986584</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1041581196014352</v>
+      </c>
+      <c r="C64">
+        <v>29.97575049507094</v>
+      </c>
+      <c r="D64">
+        <v>54.56775049507094</v>
+      </c>
+      <c r="E64">
+        <v>-5.938000000000002</v>
+      </c>
+      <c r="F64">
+        <v>27.962</v>
+      </c>
+      <c r="G64">
+        <v>3.37</v>
+      </c>
+      <c r="H64">
+        <v>11.2</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>5.05</v>
+      </c>
+      <c r="K64">
+        <v>0.073</v>
+      </c>
+      <c r="L64">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M64">
+        <v>1.9629324</v>
+      </c>
+      <c r="N64">
+        <v>3.0140676</v>
+      </c>
+      <c r="O64">
+        <v>0.60281352</v>
+      </c>
+      <c r="P64">
+        <v>2.41125408</v>
+      </c>
+      <c r="Q64">
+        <v>2.48425408</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1824708410564084</v>
+      </c>
+      <c r="T64">
+        <v>1.28467109165008</v>
+      </c>
+      <c r="U64">
+        <v>0.0702</v>
+      </c>
+      <c r="V64">
+        <v>0.2</v>
+      </c>
+      <c r="W64">
+        <v>0.05616</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>2.53549230732551</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1065758736662721</v>
+      </c>
+      <c r="C65">
+        <v>27.57816694798021</v>
+      </c>
+      <c r="D65">
+        <v>52.62116694798021</v>
+      </c>
+      <c r="E65">
+        <v>-5.487000000000002</v>
+      </c>
+      <c r="F65">
+        <v>28.413</v>
+      </c>
+      <c r="G65">
+        <v>3.37</v>
+      </c>
+      <c r="H65">
+        <v>11.2</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>5.05</v>
+      </c>
+      <c r="K65">
+        <v>0.073</v>
+      </c>
+      <c r="L65">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M65">
+        <v>2.1281337</v>
+      </c>
+      <c r="N65">
+        <v>2.8488663</v>
+      </c>
+      <c r="O65">
+        <v>0.5697732599999999</v>
+      </c>
+      <c r="P65">
+        <v>2.27909304</v>
+      </c>
+      <c r="Q65">
+        <v>2.35209304</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1860169558547894</v>
+      </c>
+      <c r="T65">
+        <v>1.316379621617995</v>
+      </c>
+      <c r="U65">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V65">
+        <v>0.2</v>
+      </c>
+      <c r="W65">
+        <v>0.05992</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>2.338668853371384</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.106662427731109</v>
+      </c>
+      <c r="C66">
+        <v>27.06005210920883</v>
+      </c>
+      <c r="D66">
+        <v>52.55405210920883</v>
+      </c>
+      <c r="E66">
+        <v>-5.036000000000001</v>
+      </c>
+      <c r="F66">
+        <v>28.864</v>
+      </c>
+      <c r="G66">
+        <v>3.37</v>
+      </c>
+      <c r="H66">
+        <v>11.2</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>5.05</v>
+      </c>
+      <c r="K66">
+        <v>0.073</v>
+      </c>
+      <c r="L66">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M66">
+        <v>2.1619136</v>
+      </c>
+      <c r="N66">
+        <v>2.8150864</v>
+      </c>
+      <c r="O66">
+        <v>0.56301728</v>
+      </c>
+      <c r="P66">
+        <v>2.25206912</v>
+      </c>
+      <c r="Q66">
+        <v>2.32506912</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1897600770308583</v>
+      </c>
+      <c r="T66">
+        <v>1.349849736584128</v>
+      </c>
+      <c r="U66">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V66">
+        <v>0.2</v>
+      </c>
+      <c r="W66">
+        <v>0.05992</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>2.302127152537456</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1067489817959459</v>
+      </c>
+      <c r="C67">
+        <v>26.54210825348834</v>
+      </c>
+      <c r="D67">
+        <v>52.48710825348834</v>
+      </c>
+      <c r="E67">
+        <v>-4.585000000000001</v>
+      </c>
+      <c r="F67">
+        <v>29.315</v>
+      </c>
+      <c r="G67">
+        <v>3.37</v>
+      </c>
+      <c r="H67">
+        <v>11.2</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>5.05</v>
+      </c>
+      <c r="K67">
+        <v>0.073</v>
+      </c>
+      <c r="L67">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M67">
+        <v>2.1956935</v>
+      </c>
+      <c r="N67">
+        <v>2.7813065</v>
+      </c>
+      <c r="O67">
+        <v>0.5562613</v>
+      </c>
+      <c r="P67">
+        <v>2.2250452</v>
+      </c>
+      <c r="Q67">
+        <v>2.2980452</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1937170908455597</v>
+      </c>
+      <c r="T67">
+        <v>1.385232429548325</v>
+      </c>
+      <c r="U67">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V67">
+        <v>0.2</v>
+      </c>
+      <c r="W67">
+        <v>0.05992</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>2.266709811729188</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1068355358607828</v>
+      </c>
+      <c r="C68">
+        <v>26.02433472825042</v>
+      </c>
+      <c r="D68">
+        <v>52.42033472825042</v>
+      </c>
+      <c r="E68">
+        <v>-4.134</v>
+      </c>
+      <c r="F68">
+        <v>29.766</v>
+      </c>
+      <c r="G68">
+        <v>3.37</v>
+      </c>
+      <c r="H68">
+        <v>11.2</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>5.05</v>
+      </c>
+      <c r="K68">
+        <v>0.073</v>
+      </c>
+      <c r="L68">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M68">
+        <v>2.2294734</v>
+      </c>
+      <c r="N68">
+        <v>2.7475266</v>
+      </c>
+      <c r="O68">
+        <v>0.54950532</v>
+      </c>
+      <c r="P68">
+        <v>2.19802128</v>
+      </c>
+      <c r="Q68">
+        <v>2.27102128</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.197906870178773</v>
+      </c>
+      <c r="T68">
+        <v>1.422696457392769</v>
+      </c>
+      <c r="U68">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V68">
+        <v>0.2</v>
+      </c>
+      <c r="W68">
+        <v>0.05992</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>2.232365723672684</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1069220899256197</v>
+      </c>
+      <c r="C69">
+        <v>25.50673088424335</v>
+      </c>
+      <c r="D69">
+        <v>52.35373088424335</v>
+      </c>
+      <c r="E69">
+        <v>-3.683</v>
+      </c>
+      <c r="F69">
+        <v>30.217</v>
+      </c>
+      <c r="G69">
+        <v>3.37</v>
+      </c>
+      <c r="H69">
+        <v>11.2</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>5.05</v>
+      </c>
+      <c r="K69">
+        <v>0.073</v>
+      </c>
+      <c r="L69">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M69">
+        <v>2.2632533</v>
+      </c>
+      <c r="N69">
+        <v>2.7137467</v>
+      </c>
+      <c r="O69">
+        <v>0.54274934</v>
+      </c>
+      <c r="P69">
+        <v>2.17099736</v>
+      </c>
+      <c r="Q69">
+        <v>2.24399736</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.202350575532181</v>
+      </c>
+      <c r="T69">
+        <v>1.462431032379301</v>
+      </c>
+      <c r="U69">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V69">
+        <v>0.2</v>
+      </c>
+      <c r="W69">
+        <v>0.05992</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>2.199046832274584</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1070086439904566</v>
+      </c>
+      <c r="C70">
+        <v>24.98929607551087</v>
+      </c>
+      <c r="D70">
+        <v>52.28729607551087</v>
+      </c>
+      <c r="E70">
+        <v>-3.231999999999999</v>
+      </c>
+      <c r="F70">
+        <v>30.668</v>
+      </c>
+      <c r="G70">
+        <v>3.37</v>
+      </c>
+      <c r="H70">
+        <v>11.2</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>5.05</v>
+      </c>
+      <c r="K70">
+        <v>0.073</v>
+      </c>
+      <c r="L70">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M70">
+        <v>2.2970332</v>
+      </c>
+      <c r="N70">
+        <v>2.6799668</v>
+      </c>
+      <c r="O70">
+        <v>0.53599336</v>
+      </c>
+      <c r="P70">
+        <v>2.14397344</v>
+      </c>
+      <c r="Q70">
+        <v>2.21697344</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2070720124701769</v>
+      </c>
+      <c r="T70">
+        <v>1.504649018302491</v>
+      </c>
+      <c r="U70">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V70">
+        <v>0.2</v>
+      </c>
+      <c r="W70">
+        <v>0.05992</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>2.166707908270546</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1070951980552935</v>
+      </c>
+      <c r="C71">
+        <v>24.47202965937129</v>
+      </c>
+      <c r="D71">
+        <v>52.2210296593713</v>
+      </c>
+      <c r="E71">
+        <v>-2.780999999999999</v>
+      </c>
+      <c r="F71">
+        <v>31.119</v>
+      </c>
+      <c r="G71">
+        <v>3.37</v>
+      </c>
+      <c r="H71">
+        <v>11.2</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>5.05</v>
+      </c>
+      <c r="K71">
+        <v>0.073</v>
+      </c>
+      <c r="L71">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M71">
+        <v>2.3308131</v>
+      </c>
+      <c r="N71">
+        <v>2.6461869</v>
+      </c>
+      <c r="O71">
+        <v>0.52923738</v>
+      </c>
+      <c r="P71">
+        <v>2.116949519999999</v>
+      </c>
+      <c r="Q71">
+        <v>2.189949519999999</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2120980582428824</v>
+      </c>
+      <c r="T71">
+        <v>1.549590745252984</v>
+      </c>
+      <c r="U71">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V71">
+        <v>0.2</v>
+      </c>
+      <c r="W71">
+        <v>0.05992</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>2.135306344382568</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1071817521201304</v>
+      </c>
+      <c r="C72">
+        <v>23.9549309963969</v>
+      </c>
+      <c r="D72">
+        <v>52.15493099639691</v>
+      </c>
+      <c r="E72">
+        <v>-2.329999999999998</v>
+      </c>
+      <c r="F72">
+        <v>31.57</v>
+      </c>
+      <c r="G72">
+        <v>3.37</v>
+      </c>
+      <c r="H72">
+        <v>11.2</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>5.05</v>
+      </c>
+      <c r="K72">
+        <v>0.073</v>
+      </c>
+      <c r="L72">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M72">
+        <v>2.364593</v>
+      </c>
+      <c r="N72">
+        <v>2.612407</v>
+      </c>
+      <c r="O72">
+        <v>0.5224814</v>
+      </c>
+      <c r="P72">
+        <v>2.0899256</v>
+      </c>
+      <c r="Q72">
+        <v>2.1629256</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2174591737337681</v>
+      </c>
+      <c r="T72">
+        <v>1.597528587333509</v>
+      </c>
+      <c r="U72">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V72">
+        <v>0.2</v>
+      </c>
+      <c r="W72">
+        <v>0.05992</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>2.104801968034245</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1072683061849673</v>
+      </c>
+      <c r="C73">
+        <v>23.43799945039326</v>
+      </c>
+      <c r="D73">
+        <v>52.08899945039326</v>
+      </c>
+      <c r="E73">
+        <v>-1.879000000000005</v>
+      </c>
+      <c r="F73">
+        <v>32.02099999999999</v>
+      </c>
+      <c r="G73">
+        <v>3.37</v>
+      </c>
+      <c r="H73">
+        <v>11.2</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>5.05</v>
+      </c>
+      <c r="K73">
+        <v>0.073</v>
+      </c>
+      <c r="L73">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M73">
+        <v>2.398372899999999</v>
+      </c>
+      <c r="N73">
+        <v>2.5786271</v>
+      </c>
+      <c r="O73">
+        <v>0.5157254200000001</v>
+      </c>
+      <c r="P73">
+        <v>2.06290168</v>
+      </c>
+      <c r="Q73">
+        <v>2.13590168</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2231900213274735</v>
+      </c>
+      <c r="T73">
+        <v>1.648772487488553</v>
+      </c>
+      <c r="U73">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V73">
+        <v>0.2</v>
+      </c>
+      <c r="W73">
+        <v>0.05992</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>2.075156869892918</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1073548602498042</v>
+      </c>
+      <c r="C74">
+        <v>22.92123438837883</v>
+      </c>
+      <c r="D74">
+        <v>52.02323438837883</v>
+      </c>
+      <c r="E74">
+        <v>-1.428000000000004</v>
+      </c>
+      <c r="F74">
+        <v>32.47199999999999</v>
+      </c>
+      <c r="G74">
+        <v>3.37</v>
+      </c>
+      <c r="H74">
+        <v>11.2</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>5.05</v>
+      </c>
+      <c r="K74">
+        <v>0.073</v>
+      </c>
+      <c r="L74">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M74">
+        <v>2.432152799999999</v>
+      </c>
+      <c r="N74">
+        <v>2.5448472</v>
+      </c>
+      <c r="O74">
+        <v>0.50896944</v>
+      </c>
+      <c r="P74">
+        <v>2.03587776</v>
+      </c>
+      <c r="Q74">
+        <v>2.10887776</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2293302151778722</v>
+      </c>
+      <c r="T74">
+        <v>1.703676666226101</v>
+      </c>
+      <c r="U74">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V74">
+        <v>0.2</v>
+      </c>
+      <c r="W74">
+        <v>0.05992</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>2.046335246699961</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1074414143146411</v>
+      </c>
+      <c r="C75">
+        <v>22.40463518056477</v>
+      </c>
+      <c r="D75">
+        <v>51.95763518056477</v>
+      </c>
+      <c r="E75">
+        <v>-0.9770000000000039</v>
+      </c>
+      <c r="F75">
+        <v>32.92299999999999</v>
+      </c>
+      <c r="G75">
+        <v>3.37</v>
+      </c>
+      <c r="H75">
+        <v>11.2</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>5.05</v>
+      </c>
+      <c r="K75">
+        <v>0.073</v>
+      </c>
+      <c r="L75">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M75">
+        <v>2.465932699999999</v>
+      </c>
+      <c r="N75">
+        <v>2.5110673</v>
+      </c>
+      <c r="O75">
+        <v>0.50221346</v>
+      </c>
+      <c r="P75">
+        <v>2.00885384</v>
+      </c>
+      <c r="Q75">
+        <v>2.08185384</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2359252382023746</v>
+      </c>
+      <c r="T75">
+        <v>1.76264782116643</v>
+      </c>
+      <c r="U75">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V75">
+        <v>0.2</v>
+      </c>
+      <c r="W75">
+        <v>0.05992</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>2.01830325701914</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1171775683794781</v>
+      </c>
+      <c r="C76">
+        <v>15.49939640508595</v>
+      </c>
+      <c r="D76">
+        <v>45.50339640508595</v>
+      </c>
+      <c r="E76">
+        <v>-0.5260000000000034</v>
+      </c>
+      <c r="F76">
+        <v>33.374</v>
+      </c>
+      <c r="G76">
+        <v>3.37</v>
+      </c>
+      <c r="H76">
+        <v>11.2</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>5.05</v>
+      </c>
+      <c r="K76">
+        <v>0.073</v>
+      </c>
+      <c r="L76">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M76">
+        <v>3.0437088</v>
+      </c>
+      <c r="N76">
+        <v>1.9332912</v>
+      </c>
+      <c r="O76">
+        <v>0.38665824</v>
+      </c>
+      <c r="P76">
+        <v>1.54663296</v>
+      </c>
+      <c r="Q76">
+        <v>1.61963296</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2430275706903002</v>
+      </c>
+      <c r="T76">
+        <v>1.826155218794476</v>
+      </c>
+      <c r="U76">
+        <v>0.0912</v>
+      </c>
+      <c r="V76">
+        <v>0.2</v>
+      </c>
+      <c r="W76">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>1.635176137743532</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.117394522444315</v>
+      </c>
+      <c r="C77">
+        <v>14.92278781930998</v>
+      </c>
+      <c r="D77">
+        <v>45.37778781930998</v>
+      </c>
+      <c r="E77">
+        <v>-0.07500000000000284</v>
+      </c>
+      <c r="F77">
+        <v>33.825</v>
+      </c>
+      <c r="G77">
+        <v>3.37</v>
+      </c>
+      <c r="H77">
+        <v>11.2</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>5.05</v>
+      </c>
+      <c r="K77">
+        <v>0.073</v>
+      </c>
+      <c r="L77">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M77">
+        <v>3.08484</v>
+      </c>
+      <c r="N77">
+        <v>1.89216</v>
+      </c>
+      <c r="O77">
+        <v>0.3784319999999999</v>
+      </c>
+      <c r="P77">
+        <v>1.513728</v>
+      </c>
+      <c r="Q77">
+        <v>1.586728</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2506980897772598</v>
+      </c>
+      <c r="T77">
+        <v>1.894743208232767</v>
+      </c>
+      <c r="U77">
+        <v>0.0912</v>
+      </c>
+      <c r="V77">
+        <v>0.2</v>
+      </c>
+      <c r="W77">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>1.613373789240285</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1176114765091519</v>
+      </c>
+      <c r="C78">
+        <v>14.34687079000444</v>
+      </c>
+      <c r="D78">
+        <v>45.25287079000444</v>
+      </c>
+      <c r="E78">
+        <v>0.3759999999999977</v>
+      </c>
+      <c r="F78">
+        <v>34.276</v>
+      </c>
+      <c r="G78">
+        <v>3.37</v>
+      </c>
+      <c r="H78">
+        <v>11.2</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>5.05</v>
+      </c>
+      <c r="K78">
+        <v>0.073</v>
+      </c>
+      <c r="L78">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M78">
+        <v>3.1259712</v>
+      </c>
+      <c r="N78">
+        <v>1.851028799999999</v>
+      </c>
+      <c r="O78">
+        <v>0.3702057599999999</v>
+      </c>
+      <c r="P78">
+        <v>1.48082304</v>
+      </c>
+      <c r="Q78">
+        <v>1.553823039999999</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2590078187881328</v>
+      </c>
+      <c r="T78">
+        <v>1.969046863457581</v>
+      </c>
+      <c r="U78">
+        <v>0.0912</v>
+      </c>
+      <c r="V78">
+        <v>0.2</v>
+      </c>
+      <c r="W78">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>1.592145186750281</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1178284305739888</v>
+      </c>
+      <c r="C79">
+        <v>13.77163962164992</v>
+      </c>
+      <c r="D79">
+        <v>45.12863962164992</v>
+      </c>
+      <c r="E79">
+        <v>0.8269999999999982</v>
+      </c>
+      <c r="F79">
+        <v>34.727</v>
+      </c>
+      <c r="G79">
+        <v>3.37</v>
+      </c>
+      <c r="H79">
+        <v>11.2</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>5.05</v>
+      </c>
+      <c r="K79">
+        <v>0.073</v>
+      </c>
+      <c r="L79">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M79">
+        <v>3.1671024</v>
+      </c>
+      <c r="N79">
+        <v>1.8098976</v>
+      </c>
+      <c r="O79">
+        <v>0.36197952</v>
+      </c>
+      <c r="P79">
+        <v>1.44791808</v>
+      </c>
+      <c r="Q79">
+        <v>1.52091808</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.268040132930386</v>
+      </c>
+      <c r="T79">
+        <v>2.049811706093249</v>
+      </c>
+      <c r="U79">
+        <v>0.0912</v>
+      </c>
+      <c r="V79">
+        <v>0.2</v>
+      </c>
+      <c r="W79">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>1.571467976532745</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1180453846388257</v>
+      </c>
+      <c r="C80">
+        <v>13.19708868109863</v>
+      </c>
+      <c r="D80">
+        <v>45.00508868109863</v>
+      </c>
+      <c r="E80">
+        <v>1.277999999999999</v>
+      </c>
+      <c r="F80">
+        <v>35.178</v>
+      </c>
+      <c r="G80">
+        <v>3.37</v>
+      </c>
+      <c r="H80">
+        <v>11.2</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>5.05</v>
+      </c>
+      <c r="K80">
+        <v>0.073</v>
+      </c>
+      <c r="L80">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M80">
+        <v>3.2082336</v>
+      </c>
+      <c r="N80">
+        <v>1.7687664</v>
+      </c>
+      <c r="O80">
+        <v>0.3537532799999999</v>
+      </c>
+      <c r="P80">
+        <v>1.41501312</v>
+      </c>
+      <c r="Q80">
+        <v>1.48801312</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2778935665401167</v>
+      </c>
+      <c r="T80">
+        <v>2.137918807150341</v>
+      </c>
+      <c r="U80">
+        <v>0.0912</v>
+      </c>
+      <c r="V80">
+        <v>0.2</v>
+      </c>
+      <c r="W80">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>1.551320951192581</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1182623387036626</v>
+      </c>
+      <c r="C81">
+        <v>12.62321239672291</v>
+      </c>
+      <c r="D81">
+        <v>44.88221239672291</v>
+      </c>
+      <c r="E81">
+        <v>1.728999999999999</v>
+      </c>
+      <c r="F81">
+        <v>35.629</v>
+      </c>
+      <c r="G81">
+        <v>3.37</v>
+      </c>
+      <c r="H81">
+        <v>11.2</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>5.05</v>
+      </c>
+      <c r="K81">
+        <v>0.073</v>
+      </c>
+      <c r="L81">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M81">
+        <v>3.2493648</v>
+      </c>
+      <c r="N81">
+        <v>1.727635199999999</v>
+      </c>
+      <c r="O81">
+        <v>0.3455270399999999</v>
+      </c>
+      <c r="P81">
+        <v>1.38210816</v>
+      </c>
+      <c r="Q81">
+        <v>1.45510816</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2886854223983933</v>
+      </c>
+      <c r="T81">
+        <v>2.234417060689061</v>
+      </c>
+      <c r="U81">
+        <v>0.0912</v>
+      </c>
+      <c r="V81">
+        <v>0.2</v>
+      </c>
+      <c r="W81">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>1.531683977126852</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1184792927684995</v>
+      </c>
+      <c r="C82">
+        <v>12.05000525757782</v>
+      </c>
+      <c r="D82">
+        <v>44.76000525757782</v>
+      </c>
+      <c r="E82">
+        <v>2.18</v>
+      </c>
+      <c r="F82">
+        <v>36.08</v>
+      </c>
+      <c r="G82">
+        <v>3.37</v>
+      </c>
+      <c r="H82">
+        <v>11.2</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>5.05</v>
+      </c>
+      <c r="K82">
+        <v>0.073</v>
+      </c>
+      <c r="L82">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M82">
+        <v>3.290496</v>
+      </c>
+      <c r="N82">
+        <v>1.686503999999999</v>
+      </c>
+      <c r="O82">
+        <v>0.3373007999999999</v>
+      </c>
+      <c r="P82">
+        <v>1.349203199999999</v>
+      </c>
+      <c r="Q82">
+        <v>1.422203199999999</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3005564638424975</v>
+      </c>
+      <c r="T82">
+        <v>2.340565139581653</v>
+      </c>
+      <c r="U82">
+        <v>0.0912</v>
+      </c>
+      <c r="V82">
+        <v>0.2</v>
+      </c>
+      <c r="W82">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>1.512537927412767</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1656863148118155</v>
+      </c>
+      <c r="C83">
+        <v>-5.053590871383577</v>
+      </c>
+      <c r="D83">
+        <v>28.10740912861642</v>
+      </c>
+      <c r="E83">
+        <v>2.631</v>
+      </c>
+      <c r="F83">
+        <v>36.531</v>
+      </c>
+      <c r="G83">
+        <v>3.37</v>
+      </c>
+      <c r="H83">
+        <v>11.2</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>5.05</v>
+      </c>
+      <c r="K83">
+        <v>0.073</v>
+      </c>
+      <c r="L83">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M83">
+        <v>5.7207546</v>
+      </c>
+      <c r="N83">
+        <v>-0.7437546000000008</v>
+      </c>
+      <c r="O83">
+        <v>-0.1487509200000002</v>
+      </c>
+      <c r="P83">
+        <v>-0.5950036800000007</v>
+      </c>
+      <c r="Q83">
+        <v>-0.5220036800000007</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3205856223611717</v>
+      </c>
+      <c r="T83">
+        <v>2.519661195189173</v>
+      </c>
+      <c r="U83">
+        <v>0.1566</v>
+      </c>
+      <c r="V83">
+        <v>0.1739980246661865</v>
+      </c>
+      <c r="W83">
+        <v>0.1293519093372752</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.8699901233309324</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1668643148118155</v>
+      </c>
+      <c r="C84">
+        <v>-5.763136962089362</v>
+      </c>
+      <c r="D84">
+        <v>27.84886303791064</v>
+      </c>
+      <c r="E84">
+        <v>3.082000000000001</v>
+      </c>
+      <c r="F84">
+        <v>36.982</v>
+      </c>
+      <c r="G84">
+        <v>3.37</v>
+      </c>
+      <c r="H84">
+        <v>11.2</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>5.05</v>
+      </c>
+      <c r="K84">
+        <v>0.073</v>
+      </c>
+      <c r="L84">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M84">
+        <v>5.791381200000001</v>
+      </c>
+      <c r="N84">
+        <v>-0.8143812000000015</v>
+      </c>
+      <c r="O84">
+        <v>-0.1628762400000003</v>
+      </c>
+      <c r="P84">
+        <v>-0.6515049600000011</v>
+      </c>
+      <c r="Q84">
+        <v>-0.5785049600000012</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3362403791590146</v>
+      </c>
+      <c r="T84">
+        <v>2.659642372699683</v>
+      </c>
+      <c r="U84">
+        <v>0.1566</v>
+      </c>
+      <c r="V84">
+        <v>0.171876097536111</v>
+      </c>
+      <c r="W84">
+        <v>0.129684203125845</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.8593804876805551</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.1680423148118155</v>
+      </c>
+      <c r="C85">
+        <v>-6.467969932401196</v>
+      </c>
+      <c r="D85">
+        <v>27.5950300675988</v>
+      </c>
+      <c r="E85">
+        <v>3.533000000000001</v>
+      </c>
+      <c r="F85">
+        <v>37.433</v>
+      </c>
+      <c r="G85">
+        <v>3.37</v>
+      </c>
+      <c r="H85">
+        <v>11.2</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>5.05</v>
+      </c>
+      <c r="K85">
+        <v>0.073</v>
+      </c>
+      <c r="L85">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M85">
+        <v>5.862007800000001</v>
+      </c>
+      <c r="N85">
+        <v>-0.8850078000000012</v>
+      </c>
+      <c r="O85">
+        <v>-0.1770015600000003</v>
+      </c>
+      <c r="P85">
+        <v>-0.708006240000001</v>
+      </c>
+      <c r="Q85">
+        <v>-0.6350062400000011</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3537368720507214</v>
+      </c>
+      <c r="T85">
+        <v>2.816091924034958</v>
+      </c>
+      <c r="U85">
+        <v>0.1566</v>
+      </c>
+      <c r="V85">
+        <v>0.1698053011802543</v>
+      </c>
+      <c r="W85">
+        <v>0.1300084898351722</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.8490265059012714</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.1692203148118155</v>
+      </c>
+      <c r="C86">
+        <v>-7.168217493768722</v>
+      </c>
+      <c r="D86">
+        <v>27.34578250623127</v>
+      </c>
+      <c r="E86">
+        <v>3.983999999999995</v>
+      </c>
+      <c r="F86">
+        <v>37.88399999999999</v>
+      </c>
+      <c r="G86">
+        <v>3.37</v>
+      </c>
+      <c r="H86">
+        <v>11.2</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>5.05</v>
+      </c>
+      <c r="K86">
+        <v>0.073</v>
+      </c>
+      <c r="L86">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M86">
+        <v>5.9326344</v>
+      </c>
+      <c r="N86">
+        <v>-0.9556344000000001</v>
+      </c>
+      <c r="O86">
+        <v>-0.19112688</v>
+      </c>
+      <c r="P86">
+        <v>-0.7645075200000001</v>
+      </c>
+      <c r="Q86">
+        <v>-0.6915075200000002</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3734204265538912</v>
+      </c>
+      <c r="T86">
+        <v>2.992097669287142</v>
+      </c>
+      <c r="U86">
+        <v>0.1566</v>
+      </c>
+      <c r="V86">
+        <v>0.167783809499537</v>
+      </c>
+      <c r="W86">
+        <v>0.1303250554323725</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.838919047497685</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.1703983148118155</v>
+      </c>
+      <c r="C87">
+        <v>-7.86400278481447</v>
+      </c>
+      <c r="D87">
+        <v>27.10099721518552</v>
+      </c>
+      <c r="E87">
+        <v>4.434999999999995</v>
+      </c>
+      <c r="F87">
+        <v>38.33499999999999</v>
+      </c>
+      <c r="G87">
+        <v>3.37</v>
+      </c>
+      <c r="H87">
+        <v>11.2</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>5.05</v>
+      </c>
+      <c r="K87">
+        <v>0.073</v>
+      </c>
+      <c r="L87">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M87">
+        <v>6.003260999999999</v>
+      </c>
+      <c r="N87">
+        <v>-1.026261</v>
+      </c>
+      <c r="O87">
+        <v>-0.2052522</v>
+      </c>
+      <c r="P87">
+        <v>-0.8210087999999999</v>
+      </c>
+      <c r="Q87">
+        <v>-0.7480087999999999</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3957284549908173</v>
+      </c>
+      <c r="T87">
+        <v>3.191570847239618</v>
+      </c>
+      <c r="U87">
+        <v>0.1566</v>
+      </c>
+      <c r="V87">
+        <v>0.1658098823289542</v>
+      </c>
+      <c r="W87">
+        <v>0.1306341724272858</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.8290494116447711</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.1715763148118155</v>
+      </c>
+      <c r="C88">
+        <v>-8.555444574185831</v>
+      </c>
+      <c r="D88">
+        <v>26.86055542581416</v>
+      </c>
+      <c r="E88">
+        <v>4.885999999999996</v>
+      </c>
+      <c r="F88">
+        <v>38.78599999999999</v>
+      </c>
+      <c r="G88">
+        <v>3.37</v>
+      </c>
+      <c r="H88">
+        <v>11.2</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>5.05</v>
+      </c>
+      <c r="K88">
+        <v>0.073</v>
+      </c>
+      <c r="L88">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M88">
+        <v>6.0738876</v>
+      </c>
+      <c r="N88">
+        <v>-1.096887600000001</v>
+      </c>
+      <c r="O88">
+        <v>-0.2193775200000001</v>
+      </c>
+      <c r="P88">
+        <v>-0.8775100800000004</v>
+      </c>
+      <c r="Q88">
+        <v>-0.8045100800000005</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4212233446330185</v>
+      </c>
+      <c r="T88">
+        <v>3.419540193471019</v>
+      </c>
+      <c r="U88">
+        <v>0.1566</v>
+      </c>
+      <c r="V88">
+        <v>0.1638818604414082</v>
+      </c>
+      <c r="W88">
+        <v>0.1309361006548755</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.8194093022070411</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.1727543148118155</v>
+      </c>
+      <c r="C89">
+        <v>-9.242657452703863</v>
+      </c>
+      <c r="D89">
+        <v>26.62434254729613</v>
+      </c>
+      <c r="E89">
+        <v>5.336999999999996</v>
+      </c>
+      <c r="F89">
+        <v>39.23699999999999</v>
+      </c>
+      <c r="G89">
+        <v>3.37</v>
+      </c>
+      <c r="H89">
+        <v>11.2</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>5.05</v>
+      </c>
+      <c r="K89">
+        <v>0.073</v>
+      </c>
+      <c r="L89">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M89">
+        <v>6.1445142</v>
+      </c>
+      <c r="N89">
+        <v>-1.1675142</v>
+      </c>
+      <c r="O89">
+        <v>-0.2335028400000001</v>
+      </c>
+      <c r="P89">
+        <v>-0.9340113600000002</v>
+      </c>
+      <c r="Q89">
+        <v>-0.8610113600000002</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.4506405249894046</v>
+      </c>
+      <c r="T89">
+        <v>3.682581746814944</v>
+      </c>
+      <c r="U89">
+        <v>0.1566</v>
+      </c>
+      <c r="V89">
+        <v>0.1619981608961047</v>
+      </c>
+      <c r="W89">
+        <v>0.13123108800367</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.8099908044805234</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.1739323148118155</v>
+      </c>
+      <c r="C90">
+        <v>-9.925752015461796</v>
+      </c>
+      <c r="D90">
+        <v>26.3922479845382</v>
+      </c>
+      <c r="E90">
+        <v>5.787999999999997</v>
+      </c>
+      <c r="F90">
+        <v>39.688</v>
+      </c>
+      <c r="G90">
+        <v>3.37</v>
+      </c>
+      <c r="H90">
+        <v>11.2</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>5.05</v>
+      </c>
+      <c r="K90">
+        <v>0.073</v>
+      </c>
+      <c r="L90">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M90">
+        <v>6.2151408</v>
+      </c>
+      <c r="N90">
+        <v>-1.238140800000001</v>
+      </c>
+      <c r="O90">
+        <v>-0.2476281600000002</v>
+      </c>
+      <c r="P90">
+        <v>-0.9905126400000007</v>
+      </c>
+      <c r="Q90">
+        <v>-0.9175126400000008</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.4849605687385217</v>
+      </c>
+      <c r="T90">
+        <v>3.989463559049523</v>
+      </c>
+      <c r="U90">
+        <v>0.1566</v>
+      </c>
+      <c r="V90">
+        <v>0.1601572727041035</v>
+      </c>
+      <c r="W90">
+        <v>0.1315193710945374</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.8007863635205174</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2237642396450466</v>
+      </c>
+      <c r="C91">
+        <v>-17.48718871538485</v>
+      </c>
+      <c r="D91">
+        <v>19.28181128461515</v>
+      </c>
+      <c r="E91">
+        <v>6.238999999999997</v>
+      </c>
+      <c r="F91">
+        <v>40.139</v>
+      </c>
+      <c r="G91">
+        <v>3.37</v>
+      </c>
+      <c r="H91">
+        <v>11.2</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>5.05</v>
+      </c>
+      <c r="K91">
+        <v>0.073</v>
+      </c>
+      <c r="L91">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M91">
+        <v>8.3810232</v>
+      </c>
+      <c r="N91">
+        <v>-3.4040232</v>
+      </c>
+      <c r="O91">
+        <v>-0.6808046400000001</v>
+      </c>
+      <c r="P91">
+        <v>-2.72321856</v>
+      </c>
+      <c r="Q91">
+        <v>-2.65021856</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5454835734713974</v>
+      </c>
+      <c r="T91">
+        <v>4.530646126008945</v>
+      </c>
+      <c r="U91">
+        <v>0.2088</v>
+      </c>
+      <c r="V91">
+        <v>0.1187683145895599</v>
+      </c>
+      <c r="W91">
+        <v>0.1840011759136999</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.5938415729477995</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2254642396450466</v>
+      </c>
+      <c r="C92">
+        <v>-18.11379320849063</v>
+      </c>
+      <c r="D92">
+        <v>19.10620679150936</v>
+      </c>
+      <c r="E92">
+        <v>6.689999999999998</v>
+      </c>
+      <c r="F92">
+        <v>40.59</v>
+      </c>
+      <c r="G92">
+        <v>3.37</v>
+      </c>
+      <c r="H92">
+        <v>11.2</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>5.05</v>
+      </c>
+      <c r="K92">
+        <v>0.073</v>
+      </c>
+      <c r="L92">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M92">
+        <v>8.475192</v>
+      </c>
+      <c r="N92">
+        <v>-3.498192</v>
+      </c>
+      <c r="O92">
+        <v>-0.6996384000000001</v>
+      </c>
+      <c r="P92">
+        <v>-2.7985536</v>
+      </c>
+      <c r="Q92">
+        <v>-2.7255536</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.596151930818537</v>
+      </c>
+      <c r="T92">
+        <v>4.98371073860984</v>
+      </c>
+      <c r="U92">
+        <v>0.2088</v>
+      </c>
+      <c r="V92">
+        <v>0.1174486666496759</v>
+      </c>
+      <c r="W92">
+        <v>0.1842767184035477</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.5872433332483795</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2271642396450466</v>
+      </c>
+      <c r="C93">
+        <v>-18.73722801674709</v>
+      </c>
+      <c r="D93">
+        <v>18.93377198325291</v>
+      </c>
+      <c r="E93">
+        <v>7.140999999999998</v>
+      </c>
+      <c r="F93">
+        <v>41.041</v>
+      </c>
+      <c r="G93">
+        <v>3.37</v>
+      </c>
+      <c r="H93">
+        <v>11.2</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>5.05</v>
+      </c>
+      <c r="K93">
+        <v>0.073</v>
+      </c>
+      <c r="L93">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M93">
+        <v>8.5693608</v>
+      </c>
+      <c r="N93">
+        <v>-3.592360800000001</v>
+      </c>
+      <c r="O93">
+        <v>-0.7184721600000001</v>
+      </c>
+      <c r="P93">
+        <v>-2.873888640000001</v>
+      </c>
+      <c r="Q93">
+        <v>-2.800888640000001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.6580799231317078</v>
+      </c>
+      <c r="T93">
+        <v>5.537456376233156</v>
+      </c>
+      <c r="U93">
+        <v>0.2088</v>
+      </c>
+      <c r="V93">
+        <v>0.1161580219612179</v>
+      </c>
+      <c r="W93">
+        <v>0.1845462050144977</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.5807901098060895</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2288642396450466</v>
+      </c>
+      <c r="C94">
+        <v>-19.35757819241212</v>
+      </c>
+      <c r="D94">
+        <v>18.76442180758787</v>
+      </c>
+      <c r="E94">
+        <v>7.591999999999999</v>
+      </c>
+      <c r="F94">
+        <v>41.492</v>
+      </c>
+      <c r="G94">
+        <v>3.37</v>
+      </c>
+      <c r="H94">
+        <v>11.2</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>5.05</v>
+      </c>
+      <c r="K94">
+        <v>0.073</v>
+      </c>
+      <c r="L94">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M94">
+        <v>8.6635296</v>
+      </c>
+      <c r="N94">
+        <v>-3.686529600000001</v>
+      </c>
+      <c r="O94">
+        <v>-0.7373059200000003</v>
+      </c>
+      <c r="P94">
+        <v>-2.949223680000001</v>
+      </c>
+      <c r="Q94">
+        <v>-2.876223680000001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.7354899135231716</v>
+      </c>
+      <c r="T94">
+        <v>6.229638423262303</v>
+      </c>
+      <c r="U94">
+        <v>0.2088</v>
+      </c>
+      <c r="V94">
+        <v>0.1148954347659873</v>
+      </c>
+      <c r="W94">
+        <v>0.1848098332208619</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.5744771738299363</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2305642396450467</v>
+      </c>
+      <c r="C95">
+        <v>-19.97492577177283</v>
+      </c>
+      <c r="D95">
+        <v>18.59807422822717</v>
+      </c>
+      <c r="E95">
+        <v>8.042999999999999</v>
+      </c>
+      <c r="F95">
+        <v>41.943</v>
+      </c>
+      <c r="G95">
+        <v>3.37</v>
+      </c>
+      <c r="H95">
+        <v>11.2</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>5.05</v>
+      </c>
+      <c r="K95">
+        <v>0.073</v>
+      </c>
+      <c r="L95">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M95">
+        <v>8.757698400000001</v>
+      </c>
+      <c r="N95">
+        <v>-3.780698400000001</v>
+      </c>
+      <c r="O95">
+        <v>-0.7561396800000003</v>
+      </c>
+      <c r="P95">
+        <v>-3.024558720000001</v>
+      </c>
+      <c r="Q95">
+        <v>-2.951558720000001</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.8350170440264819</v>
+      </c>
+      <c r="T95">
+        <v>7.119586769442633</v>
+      </c>
+      <c r="U95">
+        <v>0.2088</v>
+      </c>
+      <c r="V95">
+        <v>0.1136599999835573</v>
+      </c>
+      <c r="W95">
+        <v>0.1850677920034333</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.5682999999177865</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2322642396450466</v>
+      </c>
+      <c r="C96">
+        <v>-20.58934990765445</v>
+      </c>
+      <c r="D96">
+        <v>18.43465009234555</v>
+      </c>
+      <c r="E96">
+        <v>8.494</v>
+      </c>
+      <c r="F96">
+        <v>42.394</v>
+      </c>
+      <c r="G96">
+        <v>3.37</v>
+      </c>
+      <c r="H96">
+        <v>11.2</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>5.05</v>
+      </c>
+      <c r="K96">
+        <v>0.073</v>
+      </c>
+      <c r="L96">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M96">
+        <v>8.851867200000001</v>
+      </c>
+      <c r="N96">
+        <v>-3.874867200000002</v>
+      </c>
+      <c r="O96">
+        <v>-0.7749734400000003</v>
+      </c>
+      <c r="P96">
+        <v>-3.099893760000001</v>
+      </c>
+      <c r="Q96">
+        <v>-3.026893760000001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.9677198846975625</v>
+      </c>
+      <c r="T96">
+        <v>8.30618456434974</v>
+      </c>
+      <c r="U96">
+        <v>0.2088</v>
+      </c>
+      <c r="V96">
+        <v>0.112450851047562</v>
+      </c>
+      <c r="W96">
+        <v>0.1853202623012691</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.56225425523781</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2339642396450466</v>
+      </c>
+      <c r="C97">
+        <v>-21.20092699500398</v>
+      </c>
+      <c r="D97">
+        <v>18.27407300499602</v>
+      </c>
+      <c r="E97">
+        <v>8.945</v>
+      </c>
+      <c r="F97">
+        <v>42.845</v>
+      </c>
+      <c r="G97">
+        <v>3.37</v>
+      </c>
+      <c r="H97">
+        <v>11.2</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>5.05</v>
+      </c>
+      <c r="K97">
+        <v>0.073</v>
+      </c>
+      <c r="L97">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M97">
+        <v>8.946036000000001</v>
+      </c>
+      <c r="N97">
+        <v>-3.969036000000002</v>
+      </c>
+      <c r="O97">
+        <v>-0.7938072000000004</v>
+      </c>
+      <c r="P97">
+        <v>-3.175228800000002</v>
+      </c>
+      <c r="Q97">
+        <v>-3.102228800000002</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.153503861637076</v>
+      </c>
+      <c r="T97">
+        <v>9.967421477219695</v>
+      </c>
+      <c r="U97">
+        <v>0.2088</v>
+      </c>
+      <c r="V97">
+        <v>0.1112671578786403</v>
+      </c>
+      <c r="W97">
+        <v>0.1855674174349399</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.5563357893932015</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2356642396450466</v>
+      </c>
+      <c r="C98">
+        <v>-21.80973078996697</v>
+      </c>
+      <c r="D98">
+        <v>18.11626921003302</v>
+      </c>
+      <c r="E98">
+        <v>9.395999999999994</v>
+      </c>
+      <c r="F98">
+        <v>43.29599999999999</v>
+      </c>
+      <c r="G98">
+        <v>3.37</v>
+      </c>
+      <c r="H98">
+        <v>11.2</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>5.05</v>
+      </c>
+      <c r="K98">
+        <v>0.073</v>
+      </c>
+      <c r="L98">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M98">
+        <v>9.0402048</v>
+      </c>
+      <c r="N98">
+        <v>-4.0632048</v>
+      </c>
+      <c r="O98">
+        <v>-0.8126409600000001</v>
+      </c>
+      <c r="P98">
+        <v>-3.25056384</v>
+      </c>
+      <c r="Q98">
+        <v>-3.17756384</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.432179827046341</v>
+      </c>
+      <c r="T98">
+        <v>12.45927684652459</v>
+      </c>
+      <c r="U98">
+        <v>0.2088</v>
+      </c>
+      <c r="V98">
+        <v>0.1101081249840711</v>
+      </c>
+      <c r="W98">
+        <v>0.1858094235033259</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.5505406249203557</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2373642396450466</v>
+      </c>
+      <c r="C99">
+        <v>-22.41583252284752</v>
+      </c>
+      <c r="D99">
+        <v>17.96116747715247</v>
+      </c>
+      <c r="E99">
+        <v>9.846999999999994</v>
+      </c>
+      <c r="F99">
+        <v>43.74699999999999</v>
+      </c>
+      <c r="G99">
+        <v>3.37</v>
+      </c>
+      <c r="H99">
+        <v>11.2</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>5.05</v>
+      </c>
+      <c r="K99">
+        <v>0.073</v>
+      </c>
+      <c r="L99">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M99">
+        <v>9.134373599999998</v>
+      </c>
+      <c r="N99">
+        <v>-4.157373599999999</v>
+      </c>
+      <c r="O99">
+        <v>-0.8314747199999998</v>
+      </c>
+      <c r="P99">
+        <v>-3.325898879999999</v>
+      </c>
+      <c r="Q99">
+        <v>-3.252898879999999</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.896639769395122</v>
+      </c>
+      <c r="T99">
+        <v>16.61236912869945</v>
+      </c>
+      <c r="U99">
+        <v>0.2088</v>
+      </c>
+      <c r="V99">
+        <v>0.108972989674957</v>
+      </c>
+      <c r="W99">
+        <v>0.186046439755869</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.5448649483747852</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2390642396450466</v>
+      </c>
+      <c r="C100">
+        <v>-23.01930100531488</v>
+      </c>
+      <c r="D100">
+        <v>17.80869899468511</v>
+      </c>
+      <c r="E100">
+        <v>10.29799999999999</v>
+      </c>
+      <c r="F100">
+        <v>44.19799999999999</v>
+      </c>
+      <c r="G100">
+        <v>3.37</v>
+      </c>
+      <c r="H100">
+        <v>11.2</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>5.05</v>
+      </c>
+      <c r="K100">
+        <v>0.073</v>
+      </c>
+      <c r="L100">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M100">
+        <v>9.228542399999998</v>
+      </c>
+      <c r="N100">
+        <v>-4.251542399999999</v>
+      </c>
+      <c r="O100">
+        <v>-0.8503084799999998</v>
+      </c>
+      <c r="P100">
+        <v>-3.401233919999999</v>
+      </c>
+      <c r="Q100">
+        <v>-3.328233919999999</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.825559654092683</v>
+      </c>
+      <c r="T100">
+        <v>24.91855369304918</v>
+      </c>
+      <c r="U100">
+        <v>0.2088</v>
+      </c>
+      <c r="V100">
+        <v>0.1078610203925595</v>
+      </c>
+      <c r="W100">
+        <v>0.1862786189420336</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.5393051019627975</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2407642396450466</v>
+      </c>
+      <c r="C101">
+        <v>-23.6202027321957</v>
+      </c>
+      <c r="D101">
+        <v>17.65879726780429</v>
+      </c>
+      <c r="E101">
+        <v>10.749</v>
+      </c>
+      <c r="F101">
+        <v>44.64899999999999</v>
+      </c>
+      <c r="G101">
+        <v>3.37</v>
+      </c>
+      <c r="H101">
+        <v>11.2</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>5.05</v>
+      </c>
+      <c r="K101">
+        <v>0.073</v>
+      </c>
+      <c r="L101">
+        <v>4.976999999999999</v>
+      </c>
+      <c r="M101">
+        <v>9.322711199999999</v>
+      </c>
+      <c r="N101">
+        <v>-4.345711199999999</v>
+      </c>
+      <c r="O101">
+        <v>-0.86914224</v>
+      </c>
+      <c r="P101">
+        <v>-3.476568959999999</v>
+      </c>
+      <c r="Q101">
+        <v>-3.403568959999999</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>5.612319308185366</v>
+      </c>
+      <c r="T101">
+        <v>49.83710738609836</v>
+      </c>
+      <c r="U101">
+        <v>0.2088</v>
+      </c>
+      <c r="V101">
+        <v>0.106771515136069</v>
+      </c>
+      <c r="W101">
+        <v>0.1865061076395888</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.533857575680345</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
